--- a/blankimport.xlsx
+++ b/blankimport.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Golang projects\src\mstorefgo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grillman\go\warehouseHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E60C02B-5C8C-44F6-ABCF-C85205F1BDA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Импорт" sheetId="1" r:id="rId1"/>
@@ -23,7 +24,7 @@
     <definedName name="список_температур">'Списки (не трогать)'!$B$2:$B$4</definedName>
     <definedName name="Тип_доставки">'Списки (не трогать)'!$D$2:$D$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="330"/>
@@ -270,7 +271,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
@@ -674,35 +675,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y1342"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.3984375" customWidth="1"/>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="37.3984375" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="37.375" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="8" customWidth="1"/>
     <col min="5" max="5" width="130.5" customWidth="1"/>
-    <col min="6" max="8" width="15.3984375" customWidth="1"/>
-    <col min="9" max="9" width="166.69921875" customWidth="1"/>
-    <col min="10" max="10" width="25.3984375" customWidth="1"/>
+    <col min="6" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="166.75" customWidth="1"/>
+    <col min="10" max="10" width="25.375" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="22.09765625" customWidth="1"/>
+    <col min="14" max="14" width="22.125" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="26.19921875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.59765625" customWidth="1"/>
+    <col min="16" max="16" width="26.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.625" customWidth="1"/>
     <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="21.8984375" customWidth="1"/>
-    <col min="20" max="20" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.875" customWidth="1"/>
+    <col min="20" max="20" width="21.875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="1017" max="1019" width="8.3984375" customWidth="1"/>
+    <col min="23" max="23" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1017" max="1019" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -779,4080 +780,4080 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F2" s="10"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="P2" s="12"/>
       <c r="R2" s="12"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="P3" s="12"/>
       <c r="R3" s="12"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F4" s="10"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="P4" s="12"/>
       <c r="R4" s="12"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="P5" s="12"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="P6" s="12"/>
       <c r="R6" s="12"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="P7" s="12"/>
       <c r="R7" s="12"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="P8" s="12"/>
       <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="P9" s="12"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="P10" s="12"/>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="P11" s="12"/>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="P12" s="12"/>
       <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R13" s="12"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R14" s="12"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R15" s="12"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R16" s="12"/>
     </row>
-    <row r="17" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R18" s="12"/>
     </row>
-    <row r="19" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R20" s="12"/>
     </row>
-    <row r="21" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="12"/>
     </row>
-    <row r="22" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R22" s="12"/>
     </row>
-    <row r="23" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R23" s="12"/>
     </row>
-    <row r="24" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R25" s="12"/>
     </row>
-    <row r="26" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R26" s="12"/>
     </row>
-    <row r="27" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R27" s="12"/>
     </row>
-    <row r="28" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R28" s="12"/>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R30" s="12"/>
     </row>
-    <row r="31" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R38" s="12"/>
     </row>
-    <row r="39" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R39" s="12"/>
     </row>
-    <row r="40" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R40" s="12"/>
     </row>
-    <row r="41" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R41" s="12"/>
     </row>
-    <row r="42" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R42" s="12"/>
     </row>
-    <row r="43" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R43" s="12"/>
     </row>
-    <row r="44" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R44" s="12"/>
     </row>
-    <row r="45" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R46" s="12"/>
     </row>
-    <row r="47" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R47" s="12"/>
     </row>
-    <row r="48" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R49" s="12"/>
     </row>
-    <row r="50" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R50" s="12"/>
     </row>
-    <row r="51" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R52" s="12"/>
     </row>
-    <row r="53" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R53" s="12"/>
     </row>
-    <row r="54" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R54" s="12"/>
     </row>
-    <row r="55" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R55" s="12"/>
     </row>
-    <row r="56" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R56" s="12"/>
     </row>
-    <row r="57" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R57" s="12"/>
     </row>
-    <row r="58" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R58" s="12"/>
     </row>
-    <row r="59" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R59" s="12"/>
     </row>
-    <row r="60" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R60" s="12"/>
     </row>
-    <row r="61" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R61" s="12"/>
     </row>
-    <row r="62" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R62" s="12"/>
     </row>
-    <row r="63" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R63" s="12"/>
     </row>
-    <row r="64" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R64" s="12"/>
     </row>
-    <row r="65" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R65" s="12"/>
     </row>
-    <row r="66" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R66" s="12"/>
     </row>
-    <row r="67" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R67" s="12"/>
     </row>
-    <row r="68" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R68" s="12"/>
     </row>
-    <row r="69" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R70" s="12"/>
     </row>
-    <row r="71" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R71" s="12"/>
     </row>
-    <row r="72" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R72" s="12"/>
     </row>
-    <row r="73" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R73" s="12"/>
     </row>
-    <row r="74" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R74" s="12"/>
     </row>
-    <row r="75" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R75" s="12"/>
     </row>
-    <row r="76" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R76" s="12"/>
     </row>
-    <row r="77" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R77" s="12"/>
     </row>
-    <row r="78" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R78" s="12"/>
     </row>
-    <row r="79" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R79" s="12"/>
     </row>
-    <row r="80" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R80" s="12"/>
     </row>
-    <row r="81" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R81" s="12"/>
     </row>
-    <row r="82" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R82" s="12"/>
     </row>
-    <row r="83" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R83" s="12"/>
     </row>
-    <row r="84" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R84" s="12"/>
     </row>
-    <row r="85" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R85" s="12"/>
     </row>
-    <row r="86" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R86" s="12"/>
     </row>
-    <row r="87" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R87" s="12"/>
     </row>
-    <row r="88" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R88" s="12"/>
     </row>
-    <row r="89" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R89" s="12"/>
     </row>
-    <row r="90" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R90" s="12"/>
     </row>
-    <row r="91" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R91" s="12"/>
     </row>
-    <row r="92" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R92" s="12"/>
     </row>
-    <row r="93" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R93" s="12"/>
     </row>
-    <row r="94" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R94" s="12"/>
     </row>
-    <row r="95" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R95" s="12"/>
     </row>
-    <row r="96" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R96" s="12"/>
     </row>
-    <row r="97" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R97" s="12"/>
     </row>
-    <row r="98" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R98" s="12"/>
     </row>
-    <row r="99" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R99" s="12"/>
     </row>
-    <row r="100" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R100" s="12"/>
     </row>
-    <row r="101" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R101" s="12"/>
     </row>
-    <row r="102" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R102" s="12"/>
     </row>
-    <row r="103" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R103" s="12"/>
     </row>
-    <row r="104" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R104" s="12"/>
     </row>
-    <row r="105" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R105" s="12"/>
     </row>
-    <row r="106" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R106" s="12"/>
     </row>
-    <row r="107" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R107" s="12"/>
     </row>
-    <row r="108" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R108" s="12"/>
     </row>
-    <row r="109" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R109" s="12"/>
     </row>
-    <row r="110" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R110" s="12"/>
     </row>
-    <row r="111" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R111" s="12"/>
     </row>
-    <row r="112" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R112" s="12"/>
     </row>
-    <row r="113" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R113" s="12"/>
     </row>
-    <row r="114" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R114" s="12"/>
     </row>
-    <row r="115" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R115" s="12"/>
     </row>
-    <row r="116" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R116" s="12"/>
     </row>
-    <row r="117" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R117" s="12"/>
     </row>
-    <row r="118" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R118" s="12"/>
     </row>
-    <row r="119" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R119" s="12"/>
     </row>
-    <row r="120" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R120" s="12"/>
     </row>
-    <row r="121" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R121" s="12"/>
     </row>
-    <row r="122" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R122" s="12"/>
     </row>
-    <row r="123" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R123" s="12"/>
     </row>
-    <row r="124" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R124" s="12"/>
     </row>
-    <row r="125" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R125" s="12"/>
     </row>
-    <row r="126" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R126" s="12"/>
     </row>
-    <row r="127" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R127" s="12"/>
     </row>
-    <row r="128" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R128" s="12"/>
     </row>
-    <row r="129" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R129" s="12"/>
     </row>
-    <row r="130" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R130" s="12"/>
     </row>
-    <row r="131" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R131" s="12"/>
     </row>
-    <row r="132" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R132" s="12"/>
     </row>
-    <row r="133" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R133" s="12"/>
     </row>
-    <row r="134" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R134" s="12"/>
     </row>
-    <row r="135" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R135" s="12"/>
     </row>
-    <row r="136" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R136" s="12"/>
     </row>
-    <row r="137" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R137" s="12"/>
     </row>
-    <row r="138" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R138" s="12"/>
     </row>
-    <row r="139" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R139" s="12"/>
     </row>
-    <row r="140" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R140" s="12"/>
     </row>
-    <row r="141" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R141" s="12"/>
     </row>
-    <row r="142" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R142" s="12"/>
     </row>
-    <row r="143" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R143" s="12"/>
     </row>
-    <row r="144" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R144" s="12"/>
     </row>
-    <row r="145" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R145" s="12"/>
     </row>
-    <row r="146" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R146" s="12"/>
     </row>
-    <row r="147" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R147" s="12"/>
     </row>
-    <row r="148" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R148" s="12"/>
     </row>
-    <row r="149" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R149" s="12"/>
     </row>
-    <row r="150" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R150" s="12"/>
     </row>
-    <row r="151" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R151" s="12"/>
     </row>
-    <row r="152" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R152" s="12"/>
     </row>
-    <row r="153" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R153" s="12"/>
     </row>
-    <row r="154" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R154" s="12"/>
     </row>
-    <row r="155" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R155" s="12"/>
     </row>
-    <row r="156" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R156" s="12"/>
     </row>
-    <row r="157" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R157" s="12"/>
     </row>
-    <row r="158" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R158" s="12"/>
     </row>
-    <row r="159" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R159" s="12"/>
     </row>
-    <row r="160" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R160" s="12"/>
     </row>
-    <row r="161" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R161" s="12"/>
     </row>
-    <row r="162" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R162" s="12"/>
     </row>
-    <row r="163" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R163" s="12"/>
     </row>
-    <row r="164" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R164" s="12"/>
     </row>
-    <row r="165" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R165" s="12"/>
     </row>
-    <row r="166" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R166" s="12"/>
     </row>
-    <row r="167" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R167" s="12"/>
     </row>
-    <row r="168" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R168" s="12"/>
     </row>
-    <row r="169" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R169" s="12"/>
     </row>
-    <row r="170" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R170" s="12"/>
     </row>
-    <row r="171" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R171" s="12"/>
     </row>
-    <row r="172" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R172" s="12"/>
     </row>
-    <row r="173" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R173" s="12"/>
     </row>
-    <row r="174" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R174" s="12"/>
     </row>
-    <row r="175" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R175" s="12"/>
     </row>
-    <row r="176" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R176" s="12"/>
     </row>
-    <row r="177" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R177" s="12"/>
     </row>
-    <row r="178" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R178" s="12"/>
     </row>
-    <row r="179" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R179" s="12"/>
     </row>
-    <row r="180" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R180" s="12"/>
     </row>
-    <row r="181" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R181" s="12"/>
     </row>
-    <row r="182" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R182" s="12"/>
     </row>
-    <row r="183" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R183" s="12"/>
     </row>
-    <row r="184" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R184" s="12"/>
     </row>
-    <row r="185" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R185" s="12"/>
     </row>
-    <row r="186" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R186" s="12"/>
     </row>
-    <row r="187" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R187" s="12"/>
     </row>
-    <row r="188" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R188" s="12"/>
     </row>
-    <row r="189" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R189" s="12"/>
     </row>
-    <row r="190" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R190" s="12"/>
     </row>
-    <row r="191" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R191" s="12"/>
     </row>
-    <row r="192" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R192" s="12"/>
     </row>
-    <row r="193" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R193" s="12"/>
     </row>
-    <row r="194" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R194" s="12"/>
     </row>
-    <row r="195" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R195" s="12"/>
     </row>
-    <row r="196" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R196" s="12"/>
     </row>
-    <row r="197" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R197" s="12"/>
     </row>
-    <row r="198" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R198" s="12"/>
     </row>
-    <row r="199" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R199" s="12"/>
     </row>
-    <row r="200" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R200" s="12"/>
     </row>
-    <row r="201" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R201" s="12"/>
     </row>
-    <row r="202" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R202" s="12"/>
     </row>
-    <row r="203" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R203" s="12"/>
     </row>
-    <row r="204" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R204" s="12"/>
     </row>
-    <row r="205" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R205" s="12"/>
     </row>
-    <row r="206" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R206" s="12"/>
     </row>
-    <row r="207" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R207" s="12"/>
     </row>
-    <row r="208" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R208" s="12"/>
     </row>
-    <row r="209" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R209" s="12"/>
     </row>
-    <row r="210" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R210" s="12"/>
     </row>
-    <row r="211" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R211" s="12"/>
     </row>
-    <row r="212" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R212" s="12"/>
     </row>
-    <row r="213" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R213" s="12"/>
     </row>
-    <row r="214" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R214" s="12"/>
     </row>
-    <row r="215" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R215" s="12"/>
     </row>
-    <row r="216" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R216" s="12"/>
     </row>
-    <row r="217" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R217" s="12"/>
     </row>
-    <row r="218" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R218" s="12"/>
     </row>
-    <row r="219" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R219" s="12"/>
     </row>
-    <row r="220" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R220" s="12"/>
     </row>
-    <row r="221" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R221" s="12"/>
     </row>
-    <row r="222" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R222" s="12"/>
     </row>
-    <row r="223" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R223" s="12"/>
     </row>
-    <row r="224" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R224" s="12"/>
     </row>
-    <row r="225" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R225" s="12"/>
     </row>
-    <row r="226" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R226" s="12"/>
     </row>
-    <row r="227" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R227" s="12"/>
     </row>
-    <row r="228" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R228" s="12"/>
     </row>
-    <row r="229" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R229" s="12"/>
     </row>
-    <row r="230" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R230" s="12"/>
     </row>
-    <row r="231" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R231" s="12"/>
     </row>
-    <row r="232" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R232" s="12"/>
     </row>
-    <row r="233" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R233" s="12"/>
     </row>
-    <row r="234" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R234" s="12"/>
     </row>
-    <row r="235" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R235" s="12"/>
     </row>
-    <row r="236" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R236" s="12"/>
     </row>
-    <row r="237" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R237" s="12"/>
     </row>
-    <row r="238" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R238" s="12"/>
     </row>
-    <row r="239" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R239" s="12"/>
     </row>
-    <row r="240" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R240" s="12"/>
     </row>
-    <row r="241" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R241" s="12"/>
     </row>
-    <row r="242" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R242" s="12"/>
     </row>
-    <row r="243" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R243" s="12"/>
     </row>
-    <row r="244" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R244" s="12"/>
     </row>
-    <row r="245" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R245" s="12"/>
     </row>
-    <row r="246" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R246" s="12"/>
     </row>
-    <row r="247" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R247" s="12"/>
     </row>
-    <row r="248" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R248" s="12"/>
     </row>
-    <row r="249" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R249" s="12"/>
     </row>
-    <row r="250" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R250" s="12"/>
     </row>
-    <row r="251" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R251" s="12"/>
     </row>
-    <row r="252" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R252" s="12"/>
     </row>
-    <row r="253" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R253" s="12"/>
     </row>
-    <row r="254" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R254" s="12"/>
     </row>
-    <row r="255" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R255" s="12"/>
     </row>
-    <row r="256" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R256" s="12"/>
     </row>
-    <row r="257" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R257" s="12"/>
     </row>
-    <row r="258" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R258" s="12"/>
     </row>
-    <row r="259" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R259" s="12"/>
     </row>
-    <row r="260" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R260" s="12"/>
     </row>
-    <row r="261" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R261" s="12"/>
     </row>
-    <row r="262" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R262" s="12"/>
     </row>
-    <row r="263" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R263" s="12"/>
     </row>
-    <row r="264" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R264" s="12"/>
     </row>
-    <row r="265" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R265" s="12"/>
     </row>
-    <row r="266" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R266" s="12"/>
     </row>
-    <row r="267" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R267" s="12"/>
     </row>
-    <row r="268" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R268" s="12"/>
     </row>
-    <row r="269" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R269" s="12"/>
     </row>
-    <row r="270" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R270" s="12"/>
     </row>
-    <row r="271" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R271" s="12"/>
     </row>
-    <row r="272" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R272" s="12"/>
     </row>
-    <row r="273" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R273" s="12"/>
     </row>
-    <row r="274" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R274" s="12"/>
     </row>
-    <row r="275" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R275" s="12"/>
     </row>
-    <row r="276" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="276" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R276" s="12"/>
     </row>
-    <row r="277" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R277" s="12"/>
     </row>
-    <row r="278" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R278" s="12"/>
     </row>
-    <row r="279" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R279" s="12"/>
     </row>
-    <row r="280" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R280" s="12"/>
     </row>
-    <row r="281" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R281" s="12"/>
     </row>
-    <row r="282" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R282" s="12"/>
     </row>
-    <row r="283" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R283" s="12"/>
     </row>
-    <row r="284" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R284" s="12"/>
     </row>
-    <row r="285" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="285" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R285" s="12"/>
     </row>
-    <row r="286" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R286" s="12"/>
     </row>
-    <row r="287" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R287" s="12"/>
     </row>
-    <row r="288" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R288" s="12"/>
     </row>
-    <row r="289" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="289" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R289" s="12"/>
     </row>
-    <row r="290" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R290" s="12"/>
     </row>
-    <row r="291" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R291" s="12"/>
     </row>
-    <row r="292" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R292" s="12"/>
     </row>
-    <row r="293" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R293" s="12"/>
     </row>
-    <row r="294" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R294" s="12"/>
     </row>
-    <row r="295" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R295" s="12"/>
     </row>
-    <row r="296" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R296" s="12"/>
     </row>
-    <row r="297" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R297" s="12"/>
     </row>
-    <row r="298" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R298" s="12"/>
     </row>
-    <row r="299" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R299" s="12"/>
     </row>
-    <row r="300" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R300" s="12"/>
     </row>
-    <row r="301" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R301" s="12"/>
     </row>
-    <row r="302" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="302" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R302" s="12"/>
     </row>
-    <row r="303" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R303" s="12"/>
     </row>
-    <row r="304" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="304" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R304" s="12"/>
     </row>
-    <row r="305" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R305" s="12"/>
     </row>
-    <row r="306" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R306" s="12"/>
     </row>
-    <row r="307" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R307" s="12"/>
     </row>
-    <row r="308" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R308" s="12"/>
     </row>
-    <row r="309" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R309" s="12"/>
     </row>
-    <row r="310" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R310" s="12"/>
     </row>
-    <row r="311" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R311" s="12"/>
     </row>
-    <row r="312" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R312" s="12"/>
     </row>
-    <row r="313" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R313" s="12"/>
     </row>
-    <row r="314" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R314" s="12"/>
     </row>
-    <row r="315" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="315" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R315" s="12"/>
     </row>
-    <row r="316" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R316" s="12"/>
     </row>
-    <row r="317" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R317" s="12"/>
     </row>
-    <row r="318" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R318" s="12"/>
     </row>
-    <row r="319" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R319" s="12"/>
     </row>
-    <row r="320" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R320" s="12"/>
     </row>
-    <row r="321" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R321" s="12"/>
     </row>
-    <row r="322" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R322" s="12"/>
     </row>
-    <row r="323" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R323" s="12"/>
     </row>
-    <row r="324" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R324" s="12"/>
     </row>
-    <row r="325" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R325" s="12"/>
     </row>
-    <row r="326" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R326" s="12"/>
     </row>
-    <row r="327" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R327" s="12"/>
     </row>
-    <row r="328" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R328" s="12"/>
     </row>
-    <row r="329" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R329" s="12"/>
     </row>
-    <row r="330" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R330" s="12"/>
     </row>
-    <row r="331" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R331" s="12"/>
     </row>
-    <row r="332" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R332" s="12"/>
     </row>
-    <row r="333" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R333" s="12"/>
     </row>
-    <row r="334" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R334" s="12"/>
     </row>
-    <row r="335" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R335" s="12"/>
     </row>
-    <row r="336" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R336" s="12"/>
     </row>
-    <row r="337" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R337" s="12"/>
     </row>
-    <row r="338" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R338" s="12"/>
     </row>
-    <row r="339" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R339" s="12"/>
     </row>
-    <row r="340" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="340" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R340" s="12"/>
     </row>
-    <row r="341" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R341" s="12"/>
     </row>
-    <row r="342" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="342" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R342" s="12"/>
     </row>
-    <row r="343" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R343" s="12"/>
     </row>
-    <row r="344" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R344" s="12"/>
     </row>
-    <row r="345" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R345" s="12"/>
     </row>
-    <row r="346" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R346" s="12"/>
     </row>
-    <row r="347" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R347" s="12"/>
     </row>
-    <row r="348" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R348" s="12"/>
     </row>
-    <row r="349" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R349" s="12"/>
     </row>
-    <row r="350" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R350" s="12"/>
     </row>
-    <row r="351" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R351" s="12"/>
     </row>
-    <row r="352" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R352" s="12"/>
     </row>
-    <row r="353" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R353" s="12"/>
     </row>
-    <row r="354" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R354" s="12"/>
     </row>
-    <row r="355" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R355" s="12"/>
     </row>
-    <row r="356" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R356" s="12"/>
     </row>
-    <row r="357" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R357" s="12"/>
     </row>
-    <row r="358" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R358" s="12"/>
     </row>
-    <row r="359" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R359" s="12"/>
     </row>
-    <row r="360" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R360" s="12"/>
     </row>
-    <row r="361" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R361" s="12"/>
     </row>
-    <row r="362" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R362" s="12"/>
     </row>
-    <row r="363" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R363" s="12"/>
     </row>
-    <row r="364" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="364" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R364" s="12"/>
     </row>
-    <row r="365" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="365" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R365" s="12"/>
     </row>
-    <row r="366" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="366" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R366" s="12"/>
     </row>
-    <row r="367" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="367" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R367" s="12"/>
     </row>
-    <row r="368" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="368" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R368" s="12"/>
     </row>
-    <row r="369" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R369" s="12"/>
     </row>
-    <row r="370" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R370" s="12"/>
     </row>
-    <row r="371" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R371" s="12"/>
     </row>
-    <row r="372" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R372" s="12"/>
     </row>
-    <row r="373" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R373" s="12"/>
     </row>
-    <row r="374" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R374" s="12"/>
     </row>
-    <row r="375" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R375" s="12"/>
     </row>
-    <row r="376" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R376" s="12"/>
     </row>
-    <row r="377" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R377" s="12"/>
     </row>
-    <row r="378" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R378" s="12"/>
     </row>
-    <row r="379" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R379" s="12"/>
     </row>
-    <row r="380" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R380" s="12"/>
     </row>
-    <row r="381" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="381" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R381" s="12"/>
     </row>
-    <row r="382" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="382" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R382" s="12"/>
     </row>
-    <row r="383" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R383" s="12"/>
     </row>
-    <row r="384" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R384" s="12"/>
     </row>
-    <row r="385" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R385" s="12"/>
     </row>
-    <row r="386" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R386" s="12"/>
     </row>
-    <row r="387" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R387" s="12"/>
     </row>
-    <row r="388" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R388" s="12"/>
     </row>
-    <row r="389" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="389" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R389" s="12"/>
     </row>
-    <row r="390" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="390" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R390" s="12"/>
     </row>
-    <row r="391" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="391" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R391" s="12"/>
     </row>
-    <row r="392" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="392" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R392" s="12"/>
     </row>
-    <row r="393" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="393" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R393" s="12"/>
     </row>
-    <row r="394" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="394" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R394" s="12"/>
     </row>
-    <row r="395" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="395" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R395" s="12"/>
     </row>
-    <row r="396" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="396" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R396" s="12"/>
     </row>
-    <row r="397" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="397" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R397" s="12"/>
     </row>
-    <row r="398" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="398" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R398" s="12"/>
     </row>
-    <row r="399" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="399" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R399" s="12"/>
     </row>
-    <row r="400" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="400" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R400" s="12"/>
     </row>
-    <row r="401" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="401" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R401" s="12"/>
     </row>
-    <row r="402" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="402" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R402" s="12"/>
     </row>
-    <row r="403" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="403" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R403" s="12"/>
     </row>
-    <row r="404" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="404" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R404" s="12"/>
     </row>
-    <row r="405" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="405" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R405" s="12"/>
     </row>
-    <row r="406" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="406" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R406" s="12"/>
     </row>
-    <row r="407" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="407" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R407" s="12"/>
     </row>
-    <row r="408" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="408" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R408" s="12"/>
     </row>
-    <row r="409" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="409" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R409" s="12"/>
     </row>
-    <row r="410" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="410" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R410" s="12"/>
     </row>
-    <row r="411" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="411" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R411" s="12"/>
     </row>
-    <row r="412" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="412" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R412" s="12"/>
     </row>
-    <row r="413" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="413" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R413" s="12"/>
     </row>
-    <row r="414" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="414" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R414" s="12"/>
     </row>
-    <row r="415" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="415" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R415" s="12"/>
     </row>
-    <row r="416" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="416" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R416" s="12"/>
     </row>
-    <row r="417" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="417" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R417" s="12"/>
     </row>
-    <row r="418" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="418" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R418" s="12"/>
     </row>
-    <row r="419" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="419" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R419" s="12"/>
     </row>
-    <row r="420" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="420" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R420" s="12"/>
     </row>
-    <row r="421" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="421" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R421" s="12"/>
     </row>
-    <row r="422" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="422" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R422" s="12"/>
     </row>
-    <row r="423" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="423" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R423" s="12"/>
     </row>
-    <row r="424" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="424" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R424" s="12"/>
     </row>
-    <row r="425" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="425" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R425" s="12"/>
     </row>
-    <row r="426" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="426" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R426" s="12"/>
     </row>
-    <row r="427" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="427" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R427" s="12"/>
     </row>
-    <row r="428" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="428" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R428" s="12"/>
     </row>
-    <row r="429" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="429" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R429" s="12"/>
     </row>
-    <row r="430" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="430" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R430" s="12"/>
     </row>
-    <row r="431" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="431" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R431" s="12"/>
     </row>
-    <row r="432" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="432" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R432" s="12"/>
     </row>
-    <row r="433" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="433" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R433" s="12"/>
     </row>
-    <row r="434" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="434" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R434" s="12"/>
     </row>
-    <row r="435" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="435" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R435" s="12"/>
     </row>
-    <row r="436" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="436" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R436" s="12"/>
     </row>
-    <row r="437" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="437" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R437" s="12"/>
     </row>
-    <row r="438" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="438" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R438" s="12"/>
     </row>
-    <row r="439" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="439" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R439" s="12"/>
     </row>
-    <row r="440" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="440" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R440" s="12"/>
     </row>
-    <row r="441" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="441" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R441" s="12"/>
     </row>
-    <row r="442" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="442" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R442" s="12"/>
     </row>
-    <row r="443" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="443" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R443" s="12"/>
     </row>
-    <row r="444" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="444" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R444" s="12"/>
     </row>
-    <row r="445" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="445" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R445" s="12"/>
     </row>
-    <row r="446" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="446" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R446" s="12"/>
     </row>
-    <row r="447" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="447" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R447" s="12"/>
     </row>
-    <row r="448" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="448" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R448" s="12"/>
     </row>
-    <row r="449" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="449" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R449" s="12"/>
     </row>
-    <row r="450" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="450" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R450" s="12"/>
     </row>
-    <row r="451" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="451" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R451" s="12"/>
     </row>
-    <row r="452" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="452" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R452" s="12"/>
     </row>
-    <row r="453" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="453" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R453" s="12"/>
     </row>
-    <row r="454" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="454" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R454" s="12"/>
     </row>
-    <row r="455" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="455" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R455" s="12"/>
     </row>
-    <row r="456" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="456" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R456" s="12"/>
     </row>
-    <row r="457" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="457" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R457" s="12"/>
     </row>
-    <row r="458" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="458" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R458" s="12"/>
     </row>
-    <row r="459" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="459" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R459" s="12"/>
     </row>
-    <row r="460" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="460" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R460" s="12"/>
     </row>
-    <row r="461" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="461" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R461" s="12"/>
     </row>
-    <row r="462" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="462" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R462" s="12"/>
     </row>
-    <row r="463" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="463" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R463" s="12"/>
     </row>
-    <row r="464" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="464" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R464" s="12"/>
     </row>
-    <row r="465" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="465" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R465" s="12"/>
     </row>
-    <row r="466" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="466" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R466" s="12"/>
     </row>
-    <row r="467" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="467" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R467" s="12"/>
     </row>
-    <row r="468" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="468" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R468" s="12"/>
     </row>
-    <row r="469" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="469" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R469" s="12"/>
     </row>
-    <row r="470" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="470" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R470" s="12"/>
     </row>
-    <row r="471" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="471" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R471" s="12"/>
     </row>
-    <row r="472" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="472" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R472" s="12"/>
     </row>
-    <row r="473" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="473" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R473" s="12"/>
     </row>
-    <row r="474" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="474" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R474" s="12"/>
     </row>
-    <row r="475" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="475" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R475" s="12"/>
     </row>
-    <row r="476" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="476" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R476" s="12"/>
     </row>
-    <row r="477" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="477" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R477" s="12"/>
     </row>
-    <row r="478" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="478" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R478" s="12"/>
     </row>
-    <row r="479" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="479" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R479" s="12"/>
     </row>
-    <row r="480" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="480" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R480" s="12"/>
     </row>
-    <row r="481" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="481" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R481" s="12"/>
     </row>
-    <row r="482" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="482" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R482" s="12"/>
     </row>
-    <row r="483" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="483" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R483" s="12"/>
     </row>
-    <row r="484" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="484" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R484" s="12"/>
     </row>
-    <row r="485" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="485" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R485" s="12"/>
     </row>
-    <row r="486" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="486" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R486" s="12"/>
     </row>
-    <row r="487" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="487" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R487" s="12"/>
     </row>
-    <row r="488" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="488" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R488" s="12"/>
     </row>
-    <row r="489" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="489" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R489" s="12"/>
     </row>
-    <row r="490" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="490" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R490" s="12"/>
     </row>
-    <row r="491" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="491" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R491" s="12"/>
     </row>
-    <row r="492" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="492" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R492" s="12"/>
     </row>
-    <row r="493" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="493" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R493" s="12"/>
     </row>
-    <row r="494" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="494" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R494" s="12"/>
     </row>
-    <row r="495" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="495" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R495" s="12"/>
     </row>
-    <row r="496" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="496" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R496" s="12"/>
     </row>
-    <row r="497" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="497" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R497" s="12"/>
     </row>
-    <row r="498" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="498" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R498" s="12"/>
     </row>
-    <row r="499" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="499" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R499" s="12"/>
     </row>
-    <row r="500" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="500" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R500" s="12"/>
     </row>
-    <row r="501" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="501" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R501" s="12"/>
     </row>
-    <row r="502" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="502" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R502" s="12"/>
     </row>
-    <row r="503" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="503" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R503" s="12"/>
     </row>
-    <row r="504" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="504" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R504" s="12"/>
     </row>
-    <row r="505" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="505" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R505" s="12"/>
     </row>
-    <row r="506" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="506" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R506" s="12"/>
     </row>
-    <row r="507" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="507" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R507" s="12"/>
     </row>
-    <row r="508" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="508" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R508" s="12"/>
     </row>
-    <row r="509" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="509" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R509" s="12"/>
     </row>
-    <row r="510" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="510" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R510" s="12"/>
     </row>
-    <row r="511" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="511" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R511" s="12"/>
     </row>
-    <row r="512" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="512" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R512" s="12"/>
     </row>
-    <row r="513" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="513" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R513" s="12"/>
     </row>
-    <row r="514" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="514" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R514" s="12"/>
     </row>
-    <row r="515" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="515" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R515" s="12"/>
     </row>
-    <row r="516" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="516" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R516" s="12"/>
     </row>
-    <row r="517" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="517" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R517" s="12"/>
     </row>
-    <row r="518" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="518" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R518" s="12"/>
     </row>
-    <row r="519" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="519" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R519" s="12"/>
     </row>
-    <row r="520" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="520" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R520" s="12"/>
     </row>
-    <row r="521" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="521" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R521" s="12"/>
     </row>
-    <row r="522" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="522" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R522" s="12"/>
     </row>
-    <row r="523" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="523" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R523" s="12"/>
     </row>
-    <row r="524" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="524" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R524" s="12"/>
     </row>
-    <row r="525" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="525" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R525" s="12"/>
     </row>
-    <row r="526" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="526" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R526" s="12"/>
     </row>
-    <row r="527" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="527" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R527" s="12"/>
     </row>
-    <row r="528" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="528" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R528" s="12"/>
     </row>
-    <row r="529" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="529" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R529" s="12"/>
     </row>
-    <row r="530" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="530" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R530" s="12"/>
     </row>
-    <row r="531" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="531" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R531" s="12"/>
     </row>
-    <row r="532" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="532" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R532" s="12"/>
     </row>
-    <row r="533" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="533" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R533" s="12"/>
     </row>
-    <row r="534" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="534" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R534" s="12"/>
     </row>
-    <row r="535" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="535" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R535" s="12"/>
     </row>
-    <row r="536" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="536" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R536" s="12"/>
     </row>
-    <row r="537" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="537" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R537" s="12"/>
     </row>
-    <row r="538" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="538" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R538" s="12"/>
     </row>
-    <row r="539" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="539" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R539" s="12"/>
     </row>
-    <row r="540" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="540" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R540" s="12"/>
     </row>
-    <row r="541" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="541" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R541" s="12"/>
     </row>
-    <row r="542" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="542" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R542" s="12"/>
     </row>
-    <row r="543" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="543" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R543" s="12"/>
     </row>
-    <row r="544" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="544" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R544" s="12"/>
     </row>
-    <row r="545" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="545" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R545" s="12"/>
     </row>
-    <row r="546" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="546" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R546" s="12"/>
     </row>
-    <row r="547" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="547" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R547" s="12"/>
     </row>
-    <row r="548" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="548" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R548" s="12"/>
     </row>
-    <row r="549" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="549" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R549" s="12"/>
     </row>
-    <row r="550" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="550" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R550" s="12"/>
     </row>
-    <row r="551" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="551" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R551" s="12"/>
     </row>
-    <row r="552" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="552" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R552" s="12"/>
     </row>
-    <row r="553" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="553" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R553" s="12"/>
     </row>
-    <row r="554" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="554" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R554" s="12"/>
     </row>
-    <row r="555" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="555" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R555" s="12"/>
     </row>
-    <row r="556" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="556" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R556" s="12"/>
     </row>
-    <row r="557" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="557" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R557" s="12"/>
     </row>
-    <row r="558" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="558" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R558" s="12"/>
     </row>
-    <row r="559" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="559" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R559" s="12"/>
     </row>
-    <row r="560" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="560" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R560" s="12"/>
     </row>
-    <row r="561" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="561" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R561" s="12"/>
     </row>
-    <row r="562" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="562" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R562" s="12"/>
     </row>
-    <row r="563" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="563" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R563" s="12"/>
     </row>
-    <row r="564" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="564" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R564" s="12"/>
     </row>
-    <row r="565" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="565" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R565" s="12"/>
     </row>
-    <row r="566" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="566" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R566" s="12"/>
     </row>
-    <row r="567" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="567" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R567" s="12"/>
     </row>
-    <row r="568" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="568" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R568" s="12"/>
     </row>
-    <row r="569" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="569" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R569" s="12"/>
     </row>
-    <row r="570" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="570" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R570" s="12"/>
     </row>
-    <row r="571" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="571" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R571" s="12"/>
     </row>
-    <row r="572" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="572" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R572" s="12"/>
     </row>
-    <row r="573" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="573" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R573" s="12"/>
     </row>
-    <row r="574" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="574" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R574" s="12"/>
     </row>
-    <row r="575" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="575" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R575" s="12"/>
     </row>
-    <row r="576" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="576" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R576" s="12"/>
     </row>
-    <row r="577" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="577" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R577" s="12"/>
     </row>
-    <row r="578" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="578" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R578" s="12"/>
     </row>
-    <row r="579" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="579" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R579" s="12"/>
     </row>
-    <row r="580" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="580" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R580" s="12"/>
     </row>
-    <row r="581" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="581" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R581" s="12"/>
     </row>
-    <row r="582" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="582" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R582" s="12"/>
     </row>
-    <row r="583" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="583" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R583" s="12"/>
     </row>
-    <row r="584" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="584" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R584" s="12"/>
     </row>
-    <row r="585" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="585" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R585" s="12"/>
     </row>
-    <row r="586" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="586" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R586" s="12"/>
     </row>
-    <row r="587" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="587" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R587" s="12"/>
     </row>
-    <row r="588" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="588" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R588" s="12"/>
     </row>
-    <row r="589" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="589" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R589" s="12"/>
     </row>
-    <row r="590" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="590" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R590" s="12"/>
     </row>
-    <row r="591" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="591" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R591" s="12"/>
     </row>
-    <row r="592" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="592" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R592" s="12"/>
     </row>
-    <row r="593" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="593" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R593" s="12"/>
     </row>
-    <row r="594" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="594" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R594" s="12"/>
     </row>
-    <row r="595" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="595" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R595" s="12"/>
     </row>
-    <row r="596" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="596" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R596" s="12"/>
     </row>
-    <row r="597" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="597" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R597" s="12"/>
     </row>
-    <row r="598" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="598" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R598" s="12"/>
     </row>
-    <row r="599" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="599" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R599" s="12"/>
     </row>
-    <row r="600" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="600" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R600" s="12"/>
     </row>
-    <row r="601" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="601" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R601" s="12"/>
     </row>
-    <row r="602" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="602" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R602" s="12"/>
     </row>
-    <row r="603" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="603" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R603" s="12"/>
     </row>
-    <row r="604" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="604" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R604" s="12"/>
     </row>
-    <row r="605" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="605" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R605" s="12"/>
     </row>
-    <row r="606" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="606" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R606" s="12"/>
     </row>
-    <row r="607" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="607" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R607" s="12"/>
     </row>
-    <row r="608" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="608" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R608" s="12"/>
     </row>
-    <row r="609" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="609" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R609" s="12"/>
     </row>
-    <row r="610" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="610" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R610" s="12"/>
     </row>
-    <row r="611" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="611" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R611" s="12"/>
     </row>
-    <row r="612" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="612" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R612" s="12"/>
     </row>
-    <row r="613" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="613" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R613" s="12"/>
     </row>
-    <row r="614" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="614" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R614" s="12"/>
     </row>
-    <row r="615" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="615" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R615" s="12"/>
     </row>
-    <row r="616" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="616" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R616" s="12"/>
     </row>
-    <row r="617" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="617" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R617" s="12"/>
     </row>
-    <row r="618" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="618" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R618" s="12"/>
     </row>
-    <row r="619" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="619" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R619" s="12"/>
     </row>
-    <row r="620" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="620" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R620" s="12"/>
     </row>
-    <row r="621" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="621" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R621" s="12"/>
     </row>
-    <row r="622" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="622" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R622" s="12"/>
     </row>
-    <row r="623" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="623" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R623" s="12"/>
     </row>
-    <row r="624" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="624" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R624" s="12"/>
     </row>
-    <row r="625" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="625" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R625" s="12"/>
     </row>
-    <row r="626" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="626" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R626" s="12"/>
     </row>
-    <row r="627" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="627" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R627" s="12"/>
     </row>
-    <row r="628" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="628" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R628" s="12"/>
     </row>
-    <row r="629" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="629" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R629" s="12"/>
     </row>
-    <row r="630" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="630" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R630" s="12"/>
     </row>
-    <row r="631" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="631" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R631" s="12"/>
     </row>
-    <row r="632" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="632" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R632" s="12"/>
     </row>
-    <row r="633" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="633" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R633" s="12"/>
     </row>
-    <row r="634" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="634" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R634" s="12"/>
     </row>
-    <row r="635" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="635" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R635" s="12"/>
     </row>
-    <row r="636" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="636" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R636" s="12"/>
     </row>
-    <row r="637" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="637" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R637" s="12"/>
     </row>
-    <row r="638" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="638" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R638" s="12"/>
     </row>
-    <row r="639" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="639" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R639" s="12"/>
     </row>
-    <row r="640" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="640" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R640" s="12"/>
     </row>
-    <row r="641" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="641" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R641" s="12"/>
     </row>
-    <row r="642" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="642" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R642" s="12"/>
     </row>
-    <row r="643" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="643" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R643" s="12"/>
     </row>
-    <row r="644" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="644" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R644" s="12"/>
     </row>
-    <row r="645" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="645" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R645" s="12"/>
     </row>
-    <row r="646" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="646" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R646" s="12"/>
     </row>
-    <row r="647" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="647" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R647" s="12"/>
     </row>
-    <row r="648" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="648" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R648" s="12"/>
     </row>
-    <row r="649" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="649" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R649" s="12"/>
     </row>
-    <row r="650" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="650" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R650" s="12"/>
     </row>
-    <row r="651" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="651" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R651" s="12"/>
     </row>
-    <row r="652" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="652" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R652" s="12"/>
     </row>
-    <row r="653" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="653" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R653" s="12"/>
     </row>
-    <row r="654" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="654" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R654" s="12"/>
     </row>
-    <row r="655" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="655" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R655" s="12"/>
     </row>
-    <row r="656" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="656" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R656" s="12"/>
     </row>
-    <row r="657" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="657" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R657" s="12"/>
     </row>
-    <row r="658" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="658" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R658" s="12"/>
     </row>
-    <row r="659" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="659" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R659" s="12"/>
     </row>
-    <row r="660" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="660" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R660" s="12"/>
     </row>
-    <row r="661" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="661" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R661" s="12"/>
     </row>
-    <row r="662" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="662" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R662" s="12"/>
     </row>
-    <row r="663" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="663" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R663" s="12"/>
     </row>
-    <row r="664" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="664" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R664" s="12"/>
     </row>
-    <row r="665" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="665" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R665" s="12"/>
     </row>
-    <row r="666" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="666" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R666" s="12"/>
     </row>
-    <row r="667" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="667" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R667" s="12"/>
     </row>
-    <row r="668" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="668" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R668" s="12"/>
     </row>
-    <row r="669" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="669" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R669" s="12"/>
     </row>
-    <row r="670" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="670" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R670" s="12"/>
     </row>
-    <row r="671" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="671" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R671" s="12"/>
     </row>
-    <row r="672" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="672" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R672" s="12"/>
     </row>
-    <row r="673" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="673" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R673" s="12"/>
     </row>
-    <row r="674" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="674" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R674" s="12"/>
     </row>
-    <row r="675" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="675" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R675" s="12"/>
     </row>
-    <row r="676" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="676" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R676" s="12"/>
     </row>
-    <row r="677" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="677" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R677" s="12"/>
     </row>
-    <row r="678" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="678" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R678" s="12"/>
     </row>
-    <row r="679" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="679" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R679" s="12"/>
     </row>
-    <row r="680" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="680" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R680" s="12"/>
     </row>
-    <row r="681" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="681" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R681" s="12"/>
     </row>
-    <row r="682" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="682" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R682" s="12"/>
     </row>
-    <row r="683" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="683" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R683" s="12"/>
     </row>
-    <row r="684" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="684" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R684" s="12"/>
     </row>
-    <row r="685" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="685" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R685" s="12"/>
     </row>
-    <row r="686" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="686" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R686" s="12"/>
     </row>
-    <row r="687" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="687" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R687" s="12"/>
     </row>
-    <row r="688" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="688" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R688" s="12"/>
     </row>
-    <row r="689" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="689" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R689" s="12"/>
     </row>
-    <row r="690" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="690" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R690" s="12"/>
     </row>
-    <row r="691" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="691" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R691" s="12"/>
     </row>
-    <row r="692" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="692" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R692" s="12"/>
     </row>
-    <row r="693" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="693" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R693" s="12"/>
     </row>
-    <row r="694" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="694" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R694" s="12"/>
     </row>
-    <row r="695" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="695" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R695" s="12"/>
     </row>
-    <row r="696" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="696" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R696" s="12"/>
     </row>
-    <row r="697" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="697" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R697" s="12"/>
     </row>
-    <row r="698" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="698" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R698" s="12"/>
     </row>
-    <row r="699" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="699" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R699" s="12"/>
     </row>
-    <row r="700" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="700" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R700" s="12"/>
     </row>
-    <row r="701" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="701" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R701" s="12"/>
     </row>
-    <row r="702" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="702" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R702" s="12"/>
     </row>
-    <row r="703" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="703" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R703" s="12"/>
     </row>
-    <row r="704" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="704" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R704" s="12"/>
     </row>
-    <row r="705" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="705" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R705" s="12"/>
     </row>
-    <row r="706" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="706" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R706" s="12"/>
     </row>
-    <row r="707" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="707" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R707" s="12"/>
     </row>
-    <row r="708" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="708" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R708" s="12"/>
     </row>
-    <row r="709" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="709" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R709" s="12"/>
     </row>
-    <row r="710" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="710" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R710" s="12"/>
     </row>
-    <row r="711" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="711" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R711" s="12"/>
     </row>
-    <row r="712" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="712" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R712" s="12"/>
     </row>
-    <row r="713" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="713" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R713" s="12"/>
     </row>
-    <row r="714" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="714" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R714" s="12"/>
     </row>
-    <row r="715" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="715" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R715" s="12"/>
     </row>
-    <row r="716" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="716" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R716" s="12"/>
     </row>
-    <row r="717" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="717" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R717" s="12"/>
     </row>
-    <row r="718" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="718" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R718" s="12"/>
     </row>
-    <row r="719" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="719" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R719" s="12"/>
     </row>
-    <row r="720" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="720" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R720" s="12"/>
     </row>
-    <row r="721" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="721" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R721" s="12"/>
     </row>
-    <row r="722" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="722" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R722" s="12"/>
     </row>
-    <row r="723" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="723" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R723" s="12"/>
     </row>
-    <row r="724" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="724" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R724" s="12"/>
     </row>
-    <row r="725" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="725" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R725" s="12"/>
     </row>
-    <row r="726" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="726" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R726" s="12"/>
     </row>
-    <row r="727" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="727" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R727" s="12"/>
     </row>
-    <row r="728" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="728" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R728" s="12"/>
     </row>
-    <row r="729" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="729" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R729" s="12"/>
     </row>
-    <row r="730" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="730" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R730" s="12"/>
     </row>
-    <row r="731" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="731" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R731" s="12"/>
     </row>
-    <row r="732" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="732" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R732" s="12"/>
     </row>
-    <row r="733" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="733" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R733" s="12"/>
     </row>
-    <row r="734" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="734" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R734" s="12"/>
     </row>
-    <row r="735" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="735" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R735" s="12"/>
     </row>
-    <row r="736" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="736" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R736" s="12"/>
     </row>
-    <row r="737" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="737" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R737" s="12"/>
     </row>
-    <row r="738" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="738" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R738" s="12"/>
     </row>
-    <row r="739" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="739" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R739" s="12"/>
     </row>
-    <row r="740" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="740" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R740" s="12"/>
     </row>
-    <row r="741" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="741" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R741" s="12"/>
     </row>
-    <row r="742" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="742" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R742" s="12"/>
     </row>
-    <row r="743" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="743" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R743" s="12"/>
     </row>
-    <row r="744" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="744" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R744" s="12"/>
     </row>
-    <row r="745" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="745" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R745" s="12"/>
     </row>
-    <row r="746" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="746" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R746" s="12"/>
     </row>
-    <row r="747" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="747" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R747" s="12"/>
     </row>
-    <row r="748" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="748" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R748" s="12"/>
     </row>
-    <row r="749" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="749" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R749" s="12"/>
     </row>
-    <row r="750" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="750" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R750" s="12"/>
     </row>
-    <row r="751" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="751" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R751" s="12"/>
     </row>
-    <row r="752" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="752" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R752" s="12"/>
     </row>
-    <row r="753" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="753" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R753" s="12"/>
     </row>
-    <row r="754" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="754" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R754" s="12"/>
     </row>
-    <row r="755" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="755" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R755" s="12"/>
     </row>
-    <row r="756" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="756" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R756" s="12"/>
     </row>
-    <row r="757" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="757" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R757" s="12"/>
     </row>
-    <row r="758" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="758" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R758" s="12"/>
     </row>
-    <row r="759" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="759" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R759" s="12"/>
     </row>
-    <row r="760" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="760" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R760" s="12"/>
     </row>
-    <row r="761" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="761" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R761" s="12"/>
     </row>
-    <row r="762" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="762" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R762" s="12"/>
     </row>
-    <row r="763" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="763" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R763" s="12"/>
     </row>
-    <row r="764" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="764" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R764" s="12"/>
     </row>
-    <row r="765" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="765" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R765" s="12"/>
     </row>
-    <row r="766" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="766" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R766" s="12"/>
     </row>
-    <row r="767" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="767" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R767" s="12"/>
     </row>
-    <row r="768" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="768" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R768" s="12"/>
     </row>
-    <row r="769" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="769" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R769" s="12"/>
     </row>
-    <row r="770" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="770" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R770" s="12"/>
     </row>
-    <row r="771" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="771" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R771" s="12"/>
     </row>
-    <row r="772" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="772" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R772" s="12"/>
     </row>
-    <row r="773" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="773" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R773" s="12"/>
     </row>
-    <row r="774" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="774" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R774" s="12"/>
     </row>
-    <row r="775" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="775" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R775" s="12"/>
     </row>
-    <row r="776" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="776" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R776" s="12"/>
     </row>
-    <row r="777" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="777" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R777" s="12"/>
     </row>
-    <row r="778" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="778" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R778" s="12"/>
     </row>
-    <row r="779" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="779" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R779" s="12"/>
     </row>
-    <row r="780" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="780" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R780" s="12"/>
     </row>
-    <row r="781" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="781" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R781" s="12"/>
     </row>
-    <row r="782" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="782" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R782" s="12"/>
     </row>
-    <row r="783" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="783" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R783" s="12"/>
     </row>
-    <row r="784" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="784" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R784" s="12"/>
     </row>
-    <row r="785" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="785" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R785" s="12"/>
     </row>
-    <row r="786" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="786" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R786" s="12"/>
     </row>
-    <row r="787" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="787" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R787" s="12"/>
     </row>
-    <row r="788" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="788" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R788" s="12"/>
     </row>
-    <row r="789" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="789" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R789" s="12"/>
     </row>
-    <row r="790" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="790" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R790" s="12"/>
     </row>
-    <row r="791" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="791" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R791" s="12"/>
     </row>
-    <row r="792" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="792" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R792" s="12"/>
     </row>
-    <row r="793" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="793" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R793" s="12"/>
     </row>
-    <row r="794" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="794" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R794" s="12"/>
     </row>
-    <row r="795" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="795" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R795" s="12"/>
     </row>
-    <row r="796" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="796" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R796" s="12"/>
     </row>
-    <row r="797" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="797" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R797" s="12"/>
     </row>
-    <row r="798" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="798" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R798" s="12"/>
     </row>
-    <row r="799" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="799" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R799" s="12"/>
     </row>
-    <row r="800" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="800" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R800" s="12"/>
     </row>
-    <row r="801" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="801" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R801" s="12"/>
     </row>
-    <row r="802" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="802" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R802" s="12"/>
     </row>
-    <row r="803" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="803" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R803" s="12"/>
     </row>
-    <row r="804" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="804" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R804" s="12"/>
     </row>
-    <row r="805" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="805" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R805" s="12"/>
     </row>
-    <row r="806" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="806" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R806" s="12"/>
     </row>
-    <row r="807" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="807" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R807" s="12"/>
     </row>
-    <row r="808" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="808" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R808" s="12"/>
     </row>
-    <row r="809" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="809" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R809" s="12"/>
     </row>
-    <row r="810" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="810" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R810" s="12"/>
     </row>
-    <row r="811" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="811" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R811" s="12"/>
     </row>
-    <row r="812" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="812" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R812" s="12"/>
     </row>
-    <row r="813" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="813" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R813" s="12"/>
     </row>
-    <row r="814" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="814" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R814" s="12"/>
     </row>
-    <row r="815" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="815" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R815" s="12"/>
     </row>
-    <row r="816" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="816" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R816" s="12"/>
     </row>
-    <row r="817" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="817" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R817" s="12"/>
     </row>
-    <row r="818" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="818" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R818" s="12"/>
     </row>
-    <row r="819" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="819" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R819" s="12"/>
     </row>
-    <row r="820" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="820" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R820" s="12"/>
     </row>
-    <row r="821" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="821" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R821" s="12"/>
     </row>
-    <row r="822" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="822" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R822" s="12"/>
     </row>
-    <row r="823" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="823" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R823" s="12"/>
     </row>
-    <row r="824" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="824" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R824" s="12"/>
     </row>
-    <row r="825" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="825" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R825" s="12"/>
     </row>
-    <row r="826" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="826" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R826" s="12"/>
     </row>
-    <row r="827" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="827" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R827" s="12"/>
     </row>
-    <row r="828" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="828" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R828" s="12"/>
     </row>
-    <row r="829" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="829" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R829" s="12"/>
     </row>
-    <row r="830" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="830" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R830" s="12"/>
     </row>
-    <row r="831" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="831" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R831" s="12"/>
     </row>
-    <row r="832" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="832" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R832" s="12"/>
     </row>
-    <row r="833" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="833" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R833" s="12"/>
     </row>
-    <row r="834" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="834" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R834" s="12"/>
     </row>
-    <row r="835" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="835" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R835" s="12"/>
     </row>
-    <row r="836" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="836" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R836" s="12"/>
     </row>
-    <row r="837" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="837" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R837" s="12"/>
     </row>
-    <row r="838" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="838" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R838" s="12"/>
     </row>
-    <row r="839" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="839" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R839" s="12"/>
     </row>
-    <row r="840" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="840" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R840" s="12"/>
     </row>
-    <row r="841" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="841" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R841" s="12"/>
     </row>
-    <row r="842" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="842" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R842" s="12"/>
     </row>
-    <row r="843" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="843" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R843" s="12"/>
     </row>
-    <row r="844" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="844" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R844" s="12"/>
     </row>
-    <row r="845" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="845" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R845" s="12"/>
     </row>
-    <row r="846" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="846" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R846" s="12"/>
     </row>
-    <row r="847" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="847" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R847" s="12"/>
     </row>
-    <row r="848" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="848" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R848" s="12"/>
     </row>
-    <row r="849" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="849" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R849" s="12"/>
     </row>
-    <row r="850" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="850" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R850" s="12"/>
     </row>
-    <row r="851" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="851" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R851" s="12"/>
     </row>
-    <row r="852" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="852" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R852" s="12"/>
     </row>
-    <row r="853" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="853" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R853" s="12"/>
     </row>
-    <row r="854" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="854" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R854" s="12"/>
     </row>
-    <row r="855" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="855" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R855" s="12"/>
     </row>
-    <row r="856" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="856" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R856" s="12"/>
     </row>
-    <row r="857" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="857" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R857" s="12"/>
     </row>
-    <row r="858" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="858" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R858" s="12"/>
     </row>
-    <row r="859" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="859" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R859" s="12"/>
     </row>
-    <row r="860" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="860" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R860" s="12"/>
     </row>
-    <row r="861" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="861" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R861" s="12"/>
     </row>
-    <row r="862" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="862" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R862" s="12"/>
     </row>
-    <row r="863" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="863" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R863" s="12"/>
     </row>
-    <row r="864" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="864" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R864" s="12"/>
     </row>
-    <row r="865" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="865" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R865" s="12"/>
     </row>
-    <row r="866" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="866" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R866" s="12"/>
     </row>
-    <row r="867" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="867" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R867" s="12"/>
     </row>
-    <row r="868" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="868" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R868" s="12"/>
     </row>
-    <row r="869" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="869" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R869" s="12"/>
     </row>
-    <row r="870" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="870" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R870" s="12"/>
     </row>
-    <row r="871" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="871" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R871" s="12"/>
     </row>
-    <row r="872" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="872" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R872" s="12"/>
     </row>
-    <row r="873" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="873" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R873" s="12"/>
     </row>
-    <row r="874" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="874" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R874" s="12"/>
     </row>
-    <row r="875" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="875" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R875" s="12"/>
     </row>
-    <row r="876" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="876" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R876" s="12"/>
     </row>
-    <row r="877" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="877" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R877" s="12"/>
     </row>
-    <row r="878" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="878" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R878" s="12"/>
     </row>
-    <row r="879" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="879" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R879" s="12"/>
     </row>
-    <row r="880" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="880" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R880" s="12"/>
     </row>
-    <row r="881" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="881" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R881" s="12"/>
     </row>
-    <row r="882" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="882" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R882" s="12"/>
     </row>
-    <row r="883" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="883" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R883" s="12"/>
     </row>
-    <row r="884" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="884" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R884" s="12"/>
     </row>
-    <row r="885" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="885" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R885" s="12"/>
     </row>
-    <row r="886" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="886" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R886" s="12"/>
     </row>
-    <row r="887" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="887" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R887" s="12"/>
     </row>
-    <row r="888" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="888" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R888" s="12"/>
     </row>
-    <row r="889" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="889" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R889" s="12"/>
     </row>
-    <row r="890" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="890" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R890" s="12"/>
     </row>
-    <row r="891" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="891" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R891" s="12"/>
     </row>
-    <row r="892" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="892" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R892" s="12"/>
     </row>
-    <row r="893" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="893" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R893" s="12"/>
     </row>
-    <row r="894" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="894" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R894" s="12"/>
     </row>
-    <row r="895" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="895" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R895" s="12"/>
     </row>
-    <row r="896" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="896" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R896" s="12"/>
     </row>
-    <row r="897" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="897" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R897" s="12"/>
     </row>
-    <row r="898" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="898" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R898" s="12"/>
     </row>
-    <row r="899" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="899" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R899" s="12"/>
     </row>
-    <row r="900" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="900" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R900" s="12"/>
     </row>
-    <row r="901" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="901" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R901" s="12"/>
     </row>
-    <row r="902" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="902" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R902" s="12"/>
     </row>
-    <row r="903" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="903" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R903" s="12"/>
     </row>
-    <row r="904" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="904" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R904" s="12"/>
     </row>
-    <row r="905" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="905" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R905" s="12"/>
     </row>
-    <row r="906" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="906" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R906" s="12"/>
     </row>
-    <row r="907" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="907" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R907" s="12"/>
     </row>
-    <row r="908" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="908" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R908" s="12"/>
     </row>
-    <row r="909" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="909" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R909" s="12"/>
     </row>
-    <row r="910" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="910" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R910" s="12"/>
     </row>
-    <row r="911" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="911" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R911" s="12"/>
     </row>
-    <row r="912" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="912" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R912" s="12"/>
     </row>
-    <row r="913" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="913" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R913" s="12"/>
     </row>
-    <row r="914" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="914" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R914" s="12"/>
     </row>
-    <row r="915" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="915" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R915" s="12"/>
     </row>
-    <row r="916" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="916" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R916" s="12"/>
     </row>
-    <row r="917" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="917" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R917" s="12"/>
     </row>
-    <row r="918" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="918" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R918" s="12"/>
     </row>
-    <row r="919" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="919" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R919" s="12"/>
     </row>
-    <row r="920" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="920" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R920" s="12"/>
     </row>
-    <row r="921" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="921" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R921" s="12"/>
     </row>
-    <row r="922" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="922" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R922" s="12"/>
     </row>
-    <row r="923" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="923" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R923" s="12"/>
     </row>
-    <row r="924" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="924" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R924" s="12"/>
     </row>
-    <row r="925" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="925" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R925" s="12"/>
     </row>
-    <row r="926" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="926" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R926" s="12"/>
     </row>
-    <row r="927" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="927" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R927" s="12"/>
     </row>
-    <row r="928" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="928" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R928" s="12"/>
     </row>
-    <row r="929" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="929" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R929" s="12"/>
     </row>
-    <row r="930" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="930" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R930" s="12"/>
     </row>
-    <row r="931" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="931" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R931" s="12"/>
     </row>
-    <row r="932" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="932" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R932" s="12"/>
     </row>
-    <row r="933" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="933" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R933" s="12"/>
     </row>
-    <row r="934" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="934" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R934" s="12"/>
     </row>
-    <row r="935" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="935" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R935" s="12"/>
     </row>
-    <row r="936" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="936" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R936" s="12"/>
     </row>
-    <row r="937" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="937" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R937" s="12"/>
     </row>
-    <row r="938" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="938" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R938" s="12"/>
     </row>
-    <row r="939" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="939" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R939" s="12"/>
     </row>
-    <row r="940" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="940" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R940" s="12"/>
     </row>
-    <row r="941" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="941" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R941" s="12"/>
     </row>
-    <row r="942" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="942" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R942" s="12"/>
     </row>
-    <row r="943" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="943" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R943" s="12"/>
     </row>
-    <row r="944" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="944" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R944" s="12"/>
     </row>
-    <row r="945" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="945" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R945" s="12"/>
     </row>
-    <row r="946" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="946" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R946" s="12"/>
     </row>
-    <row r="947" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="947" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R947" s="12"/>
     </row>
-    <row r="948" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="948" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R948" s="12"/>
     </row>
-    <row r="949" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="949" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R949" s="12"/>
     </row>
-    <row r="950" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="950" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R950" s="12"/>
     </row>
-    <row r="951" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="951" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R951" s="12"/>
     </row>
-    <row r="952" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="952" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R952" s="12"/>
     </row>
-    <row r="953" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="953" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R953" s="12"/>
     </row>
-    <row r="954" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="954" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R954" s="12"/>
     </row>
-    <row r="955" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="955" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R955" s="12"/>
     </row>
-    <row r="956" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="956" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R956" s="12"/>
     </row>
-    <row r="957" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="957" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R957" s="12"/>
     </row>
-    <row r="958" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="958" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R958" s="12"/>
     </row>
-    <row r="959" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="959" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R959" s="12"/>
     </row>
-    <row r="960" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="960" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R960" s="12"/>
     </row>
-    <row r="961" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="961" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R961" s="12"/>
     </row>
-    <row r="962" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="962" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R962" s="12"/>
     </row>
-    <row r="963" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="963" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R963" s="12"/>
     </row>
-    <row r="964" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="964" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R964" s="12"/>
     </row>
-    <row r="965" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="965" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R965" s="12"/>
     </row>
-    <row r="966" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="966" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R966" s="12"/>
     </row>
-    <row r="967" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="967" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R967" s="12"/>
     </row>
-    <row r="968" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="968" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R968" s="12"/>
     </row>
-    <row r="969" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="969" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R969" s="12"/>
     </row>
-    <row r="970" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="970" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R970" s="12"/>
     </row>
-    <row r="971" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="971" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R971" s="12"/>
     </row>
-    <row r="972" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="972" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R972" s="12"/>
     </row>
-    <row r="973" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="973" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R973" s="12"/>
     </row>
-    <row r="974" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="974" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R974" s="12"/>
     </row>
-    <row r="975" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="975" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R975" s="12"/>
     </row>
-    <row r="976" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="976" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R976" s="12"/>
     </row>
-    <row r="977" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="977" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R977" s="12"/>
     </row>
-    <row r="978" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="978" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R978" s="12"/>
     </row>
-    <row r="979" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="979" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R979" s="12"/>
     </row>
-    <row r="980" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="980" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R980" s="12"/>
     </row>
-    <row r="981" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="981" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R981" s="12"/>
     </row>
-    <row r="982" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="982" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R982" s="12"/>
     </row>
-    <row r="983" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="983" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R983" s="12"/>
     </row>
-    <row r="984" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="984" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R984" s="12"/>
     </row>
-    <row r="985" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="985" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R985" s="12"/>
     </row>
-    <row r="986" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="986" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R986" s="12"/>
     </row>
-    <row r="987" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="987" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R987" s="12"/>
     </row>
-    <row r="988" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="988" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R988" s="12"/>
     </row>
-    <row r="989" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="989" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R989" s="12"/>
     </row>
-    <row r="990" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="990" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R990" s="12"/>
     </row>
-    <row r="991" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="991" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R991" s="12"/>
     </row>
-    <row r="992" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="992" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R992" s="12"/>
     </row>
-    <row r="993" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="993" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R993" s="12"/>
     </row>
-    <row r="994" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="994" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R994" s="12"/>
     </row>
-    <row r="995" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="995" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R995" s="12"/>
     </row>
-    <row r="996" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="996" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R996" s="12"/>
     </row>
-    <row r="997" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="997" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R997" s="12"/>
     </row>
-    <row r="998" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="998" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R998" s="12"/>
     </row>
-    <row r="999" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="999" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R999" s="12"/>
     </row>
-    <row r="1000" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1000" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1000" s="12"/>
     </row>
-    <row r="1001" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1001" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1001" s="12"/>
     </row>
-    <row r="1002" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1002" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1002" s="12"/>
     </row>
-    <row r="1003" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1003" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1003" s="12"/>
     </row>
-    <row r="1004" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1004" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1004" s="12"/>
     </row>
-    <row r="1005" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1005" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1005" s="12"/>
     </row>
-    <row r="1006" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1006" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1006" s="12"/>
     </row>
-    <row r="1007" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1007" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1007" s="12"/>
     </row>
-    <row r="1008" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1008" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1008" s="12"/>
     </row>
-    <row r="1009" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1009" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1009" s="12"/>
     </row>
-    <row r="1010" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1010" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1010" s="12"/>
     </row>
-    <row r="1011" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1011" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1011" s="12"/>
     </row>
-    <row r="1012" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1012" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1012" s="12"/>
     </row>
-    <row r="1013" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1013" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1013" s="12"/>
     </row>
-    <row r="1014" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1014" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1014" s="12"/>
     </row>
-    <row r="1015" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1015" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1015" s="12"/>
     </row>
-    <row r="1016" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1016" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1016" s="12"/>
     </row>
-    <row r="1017" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1017" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1017" s="12"/>
     </row>
-    <row r="1018" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1018" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1018" s="12"/>
     </row>
-    <row r="1019" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1019" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1019" s="12"/>
     </row>
-    <row r="1020" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1020" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1020" s="12"/>
     </row>
-    <row r="1021" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1021" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1021" s="12"/>
     </row>
-    <row r="1022" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1022" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1022" s="12"/>
     </row>
-    <row r="1023" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1023" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1023" s="12"/>
     </row>
-    <row r="1024" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1024" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1024" s="12"/>
     </row>
-    <row r="1025" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1025" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1025" s="12"/>
     </row>
-    <row r="1026" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1026" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1026" s="12"/>
     </row>
-    <row r="1027" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1027" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1027" s="12"/>
     </row>
-    <row r="1028" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1028" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1028" s="12"/>
     </row>
-    <row r="1029" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1029" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1029" s="12"/>
     </row>
-    <row r="1030" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1030" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1030" s="12"/>
     </row>
-    <row r="1031" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1031" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1031" s="12"/>
     </row>
-    <row r="1032" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1032" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1032" s="12"/>
     </row>
-    <row r="1033" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1033" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1033" s="12"/>
     </row>
-    <row r="1034" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1034" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1034" s="12"/>
     </row>
-    <row r="1035" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1035" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1035" s="12"/>
     </row>
-    <row r="1036" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1036" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1036" s="12"/>
     </row>
-    <row r="1037" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1037" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1037" s="12"/>
     </row>
-    <row r="1038" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1038" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1038" s="12"/>
     </row>
-    <row r="1039" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1039" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1039" s="12"/>
     </row>
-    <row r="1040" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1040" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1040" s="12"/>
     </row>
-    <row r="1041" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1041" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1041" s="12"/>
     </row>
-    <row r="1042" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1042" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1042" s="12"/>
     </row>
-    <row r="1043" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1043" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1043" s="12"/>
     </row>
-    <row r="1044" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1044" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1044" s="12"/>
     </row>
-    <row r="1045" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1045" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1045" s="12"/>
     </row>
-    <row r="1046" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1046" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1046" s="12"/>
     </row>
-    <row r="1047" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1047" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1047" s="12"/>
     </row>
-    <row r="1048" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1048" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1048" s="12"/>
     </row>
-    <row r="1049" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1049" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1049" s="12"/>
     </row>
-    <row r="1050" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1050" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1050" s="12"/>
     </row>
-    <row r="1051" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1051" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1051" s="12"/>
     </row>
-    <row r="1052" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1052" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1052" s="12"/>
     </row>
-    <row r="1053" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1053" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1053" s="12"/>
     </row>
-    <row r="1054" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1054" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1054" s="12"/>
     </row>
-    <row r="1055" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1055" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1055" s="12"/>
     </row>
-    <row r="1056" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1056" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1056" s="12"/>
     </row>
-    <row r="1057" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1057" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1057" s="12"/>
     </row>
-    <row r="1058" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1058" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1058" s="12"/>
     </row>
-    <row r="1059" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1059" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1059" s="12"/>
     </row>
-    <row r="1060" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1060" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1060" s="12"/>
     </row>
-    <row r="1061" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1061" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1061" s="12"/>
     </row>
-    <row r="1062" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1062" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1062" s="12"/>
     </row>
-    <row r="1063" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1063" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1063" s="12"/>
     </row>
-    <row r="1064" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1064" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1064" s="12"/>
     </row>
-    <row r="1065" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1065" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1065" s="12"/>
     </row>
-    <row r="1066" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1066" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1066" s="12"/>
     </row>
-    <row r="1067" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1067" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1067" s="12"/>
     </row>
-    <row r="1068" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1068" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1068" s="12"/>
     </row>
-    <row r="1069" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1069" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1069" s="12"/>
     </row>
-    <row r="1070" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1070" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1070" s="12"/>
     </row>
-    <row r="1071" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1071" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1071" s="12"/>
     </row>
-    <row r="1072" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1072" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1072" s="12"/>
     </row>
-    <row r="1073" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1073" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1073" s="12"/>
     </row>
-    <row r="1074" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1074" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1074" s="12"/>
     </row>
-    <row r="1075" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1075" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1075" s="12"/>
     </row>
-    <row r="1076" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1076" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1076" s="12"/>
     </row>
-    <row r="1077" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1077" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1077" s="12"/>
     </row>
-    <row r="1078" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1078" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1078" s="12"/>
     </row>
-    <row r="1079" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1079" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1079" s="12"/>
     </row>
-    <row r="1080" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1080" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1080" s="12"/>
     </row>
-    <row r="1081" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1081" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1081" s="12"/>
     </row>
-    <row r="1082" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1082" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1082" s="12"/>
     </row>
-    <row r="1083" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1083" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1083" s="12"/>
     </row>
-    <row r="1084" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1084" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1084" s="12"/>
     </row>
-    <row r="1085" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1085" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1085" s="12"/>
     </row>
-    <row r="1086" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1086" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1086" s="12"/>
     </row>
-    <row r="1087" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1087" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1087" s="12"/>
     </row>
-    <row r="1088" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1088" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1088" s="12"/>
     </row>
-    <row r="1089" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1089" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1089" s="12"/>
     </row>
-    <row r="1090" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1090" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1090" s="12"/>
     </row>
-    <row r="1091" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1091" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1091" s="12"/>
     </row>
-    <row r="1092" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1092" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1092" s="12"/>
     </row>
-    <row r="1093" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1093" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1093" s="12"/>
     </row>
-    <row r="1094" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1094" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1094" s="12"/>
     </row>
-    <row r="1095" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1095" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1095" s="12"/>
     </row>
-    <row r="1096" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1096" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1096" s="12"/>
     </row>
-    <row r="1097" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1097" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1097" s="12"/>
     </row>
-    <row r="1098" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1098" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1098" s="12"/>
     </row>
-    <row r="1099" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1099" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1099" s="12"/>
     </row>
-    <row r="1100" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1100" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1100" s="12"/>
     </row>
-    <row r="1101" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1101" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1101" s="12"/>
     </row>
-    <row r="1102" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1102" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1102" s="12"/>
     </row>
-    <row r="1103" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1103" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1103" s="12"/>
     </row>
-    <row r="1104" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1104" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1104" s="12"/>
     </row>
-    <row r="1105" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1105" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1105" s="12"/>
     </row>
-    <row r="1106" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1106" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1106" s="12"/>
     </row>
-    <row r="1107" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1107" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1107" s="12"/>
     </row>
-    <row r="1108" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1108" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1108" s="12"/>
     </row>
-    <row r="1109" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1109" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1109" s="12"/>
     </row>
-    <row r="1110" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1110" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1110" s="12"/>
     </row>
-    <row r="1111" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1111" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1111" s="12"/>
     </row>
-    <row r="1112" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1112" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1112" s="12"/>
     </row>
-    <row r="1113" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1113" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1113" s="12"/>
     </row>
-    <row r="1114" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1114" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1114" s="12"/>
     </row>
-    <row r="1115" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1115" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1115" s="12"/>
     </row>
-    <row r="1116" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1116" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1116" s="12"/>
     </row>
-    <row r="1117" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1117" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1117" s="12"/>
     </row>
-    <row r="1118" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1118" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1118" s="12"/>
     </row>
-    <row r="1119" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1119" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1119" s="12"/>
     </row>
-    <row r="1120" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1120" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1120" s="12"/>
     </row>
-    <row r="1121" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1121" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1121" s="12"/>
     </row>
-    <row r="1122" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1122" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1122" s="12"/>
     </row>
-    <row r="1123" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1123" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1123" s="12"/>
     </row>
-    <row r="1124" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1124" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1124" s="12"/>
     </row>
-    <row r="1125" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1125" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1125" s="12"/>
     </row>
-    <row r="1126" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1126" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1126" s="12"/>
     </row>
-    <row r="1127" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1127" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1127" s="12"/>
     </row>
-    <row r="1128" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1128" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1128" s="12"/>
     </row>
-    <row r="1129" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1129" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1129" s="12"/>
     </row>
-    <row r="1130" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1130" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1130" s="12"/>
     </row>
-    <row r="1131" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1131" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1131" s="12"/>
     </row>
-    <row r="1132" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1132" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1132" s="12"/>
     </row>
-    <row r="1133" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1133" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1133" s="12"/>
     </row>
-    <row r="1134" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1134" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1134" s="12"/>
     </row>
-    <row r="1135" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1135" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1135" s="12"/>
     </row>
-    <row r="1136" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1136" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1136" s="12"/>
     </row>
-    <row r="1137" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1137" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1137" s="12"/>
     </row>
-    <row r="1138" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1138" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1138" s="12"/>
     </row>
-    <row r="1139" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1139" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1139" s="12"/>
     </row>
-    <row r="1140" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1140" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1140" s="12"/>
     </row>
-    <row r="1141" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1141" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1141" s="12"/>
     </row>
-    <row r="1142" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1142" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1142" s="12"/>
     </row>
-    <row r="1143" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1143" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1143" s="12"/>
     </row>
-    <row r="1144" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1144" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1144" s="12"/>
     </row>
-    <row r="1145" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1145" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1145" s="12"/>
     </row>
-    <row r="1146" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1146" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1146" s="12"/>
     </row>
-    <row r="1147" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1147" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1147" s="12"/>
     </row>
-    <row r="1148" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1148" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1148" s="12"/>
     </row>
-    <row r="1149" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1149" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1149" s="12"/>
     </row>
-    <row r="1150" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1150" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1150" s="12"/>
     </row>
-    <row r="1151" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1151" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1151" s="12"/>
     </row>
-    <row r="1152" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1152" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1152" s="12"/>
     </row>
-    <row r="1153" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1153" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1153" s="12"/>
     </row>
-    <row r="1154" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1154" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1154" s="12"/>
     </row>
-    <row r="1155" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1155" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1155" s="12"/>
     </row>
-    <row r="1156" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1156" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1156" s="12"/>
     </row>
-    <row r="1157" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1157" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1157" s="12"/>
     </row>
-    <row r="1158" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1158" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1158" s="12"/>
     </row>
-    <row r="1159" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1159" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1159" s="12"/>
     </row>
-    <row r="1160" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1160" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1160" s="12"/>
     </row>
-    <row r="1161" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1161" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1161" s="12"/>
     </row>
-    <row r="1162" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1162" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1162" s="12"/>
     </row>
-    <row r="1163" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1163" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1163" s="12"/>
     </row>
-    <row r="1164" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1164" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1164" s="12"/>
     </row>
-    <row r="1165" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1165" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1165" s="12"/>
     </row>
-    <row r="1166" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1166" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1166" s="12"/>
     </row>
-    <row r="1167" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1167" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1167" s="12"/>
     </row>
-    <row r="1168" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1168" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1168" s="12"/>
     </row>
-    <row r="1169" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1169" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1169" s="12"/>
     </row>
-    <row r="1170" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1170" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1170" s="12"/>
     </row>
-    <row r="1171" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1171" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1171" s="12"/>
     </row>
-    <row r="1172" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1172" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1172" s="12"/>
     </row>
-    <row r="1173" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1173" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1173" s="12"/>
     </row>
-    <row r="1174" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1174" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1174" s="12"/>
     </row>
-    <row r="1175" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1175" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1175" s="12"/>
     </row>
-    <row r="1176" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1176" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1176" s="12"/>
     </row>
-    <row r="1177" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1177" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1177" s="12"/>
     </row>
-    <row r="1178" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1178" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1178" s="12"/>
     </row>
-    <row r="1179" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1179" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1179" s="12"/>
     </row>
-    <row r="1180" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1180" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1180" s="12"/>
     </row>
-    <row r="1181" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1181" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1181" s="12"/>
     </row>
-    <row r="1182" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1182" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1182" s="12"/>
     </row>
-    <row r="1183" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1183" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1183" s="12"/>
     </row>
-    <row r="1184" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1184" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1184" s="12"/>
     </row>
-    <row r="1185" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1185" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1185" s="12"/>
     </row>
-    <row r="1186" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1186" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1186" s="12"/>
     </row>
-    <row r="1187" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1187" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1187" s="12"/>
     </row>
-    <row r="1188" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1188" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1188" s="12"/>
     </row>
-    <row r="1189" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1189" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1189" s="12"/>
     </row>
-    <row r="1190" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1190" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1190" s="12"/>
     </row>
-    <row r="1191" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1191" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1191" s="12"/>
     </row>
-    <row r="1192" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1192" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1192" s="12"/>
     </row>
-    <row r="1193" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1193" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1193" s="12"/>
     </row>
-    <row r="1194" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1194" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1194" s="12"/>
     </row>
-    <row r="1195" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1195" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1195" s="12"/>
     </row>
-    <row r="1196" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1196" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1196" s="12"/>
     </row>
-    <row r="1197" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1197" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1197" s="12"/>
     </row>
-    <row r="1198" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1198" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1198" s="12"/>
     </row>
-    <row r="1199" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1199" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1199" s="12"/>
     </row>
-    <row r="1200" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1200" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1200" s="12"/>
     </row>
-    <row r="1201" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1201" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1201" s="12"/>
     </row>
-    <row r="1202" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1202" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1202" s="12"/>
     </row>
-    <row r="1203" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1203" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1203" s="12"/>
     </row>
-    <row r="1204" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1204" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1204" s="12"/>
     </row>
-    <row r="1205" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1205" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1205" s="12"/>
     </row>
-    <row r="1206" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1206" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1206" s="12"/>
     </row>
-    <row r="1207" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1207" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1207" s="12"/>
     </row>
-    <row r="1208" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1208" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1208" s="12"/>
     </row>
-    <row r="1209" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1209" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1209" s="12"/>
     </row>
-    <row r="1210" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1210" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1210" s="12"/>
     </row>
-    <row r="1211" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1211" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1211" s="12"/>
     </row>
-    <row r="1212" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1212" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1212" s="12"/>
     </row>
-    <row r="1213" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1213" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1213" s="12"/>
     </row>
-    <row r="1214" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1214" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1214" s="12"/>
     </row>
-    <row r="1215" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1215" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1215" s="12"/>
     </row>
-    <row r="1216" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1216" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1216" s="12"/>
     </row>
-    <row r="1217" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1217" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1217" s="12"/>
     </row>
-    <row r="1218" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1218" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1218" s="12"/>
     </row>
-    <row r="1219" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1219" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1219" s="12"/>
     </row>
-    <row r="1220" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1220" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1220" s="12"/>
     </row>
-    <row r="1221" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1221" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1221" s="12"/>
     </row>
-    <row r="1222" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1222" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1222" s="12"/>
     </row>
-    <row r="1223" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1223" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1223" s="12"/>
     </row>
-    <row r="1224" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1224" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1224" s="12"/>
     </row>
-    <row r="1225" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1225" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1225" s="12"/>
     </row>
-    <row r="1226" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1226" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1226" s="12"/>
     </row>
-    <row r="1227" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1227" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1227" s="12"/>
     </row>
-    <row r="1228" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1228" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1228" s="12"/>
     </row>
-    <row r="1229" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1229" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1229" s="12"/>
     </row>
-    <row r="1230" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1230" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1230" s="12"/>
     </row>
-    <row r="1231" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1231" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1231" s="12"/>
     </row>
-    <row r="1232" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1232" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1232" s="12"/>
     </row>
-    <row r="1233" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1233" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1233" s="12"/>
     </row>
-    <row r="1234" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1234" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1234" s="12"/>
     </row>
-    <row r="1235" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1235" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1235" s="12"/>
     </row>
-    <row r="1236" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1236" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1236" s="12"/>
     </row>
-    <row r="1237" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1237" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1237" s="12"/>
     </row>
-    <row r="1238" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1238" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1238" s="12"/>
     </row>
-    <row r="1239" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1239" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1239" s="12"/>
     </row>
-    <row r="1240" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1240" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1240" s="12"/>
     </row>
-    <row r="1241" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1241" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1241" s="12"/>
     </row>
-    <row r="1242" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1242" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1242" s="12"/>
     </row>
-    <row r="1243" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1243" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1243" s="12"/>
     </row>
-    <row r="1244" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1244" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1244" s="12"/>
     </row>
-    <row r="1245" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1245" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1245" s="12"/>
     </row>
-    <row r="1246" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1246" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1246" s="12"/>
     </row>
-    <row r="1247" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1247" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1247" s="12"/>
     </row>
-    <row r="1248" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1248" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1248" s="12"/>
     </row>
-    <row r="1249" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1249" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1249" s="12"/>
     </row>
-    <row r="1250" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1250" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1250" s="12"/>
     </row>
-    <row r="1251" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1251" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1251" s="12"/>
     </row>
-    <row r="1252" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1252" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1252" s="12"/>
     </row>
-    <row r="1253" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1253" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1253" s="12"/>
     </row>
-    <row r="1254" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1254" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1254" s="12"/>
     </row>
-    <row r="1255" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1255" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1255" s="12"/>
     </row>
-    <row r="1256" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1256" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1256" s="12"/>
     </row>
-    <row r="1257" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1257" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1257" s="12"/>
     </row>
-    <row r="1258" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1258" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1258" s="12"/>
     </row>
-    <row r="1259" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1259" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1259" s="12"/>
     </row>
-    <row r="1260" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1260" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1260" s="12"/>
     </row>
-    <row r="1261" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1261" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1261" s="12"/>
     </row>
-    <row r="1262" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1262" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1262" s="12"/>
     </row>
-    <row r="1263" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1263" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1263" s="12"/>
     </row>
-    <row r="1264" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1264" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1264" s="12"/>
     </row>
-    <row r="1265" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1265" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1265" s="12"/>
     </row>
-    <row r="1266" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1266" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1266" s="12"/>
     </row>
-    <row r="1267" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1267" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1267" s="12"/>
     </row>
-    <row r="1268" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1268" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1268" s="12"/>
     </row>
-    <row r="1269" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1269" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1269" s="12"/>
     </row>
-    <row r="1270" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1270" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1270" s="12"/>
     </row>
-    <row r="1271" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1271" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1271" s="12"/>
     </row>
-    <row r="1272" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1272" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1272" s="12"/>
     </row>
-    <row r="1273" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1273" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1273" s="12"/>
     </row>
-    <row r="1274" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1274" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1274" s="12"/>
     </row>
-    <row r="1275" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1275" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1275" s="12"/>
     </row>
-    <row r="1276" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1276" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1276" s="12"/>
     </row>
-    <row r="1277" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1277" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1277" s="12"/>
     </row>
-    <row r="1278" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1278" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1278" s="12"/>
     </row>
-    <row r="1279" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1279" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1279" s="12"/>
     </row>
-    <row r="1280" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1280" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1280" s="12"/>
     </row>
-    <row r="1281" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1281" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1281" s="12"/>
     </row>
-    <row r="1282" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1282" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1282" s="12"/>
     </row>
-    <row r="1283" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1283" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1283" s="12"/>
     </row>
-    <row r="1284" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1284" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1284" s="12"/>
     </row>
-    <row r="1285" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1285" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1285" s="12"/>
     </row>
-    <row r="1286" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1286" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1286" s="12"/>
     </row>
-    <row r="1287" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1287" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1287" s="12"/>
     </row>
-    <row r="1288" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1288" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1288" s="12"/>
     </row>
-    <row r="1289" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1289" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1289" s="12"/>
     </row>
-    <row r="1290" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1290" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1290" s="12"/>
     </row>
-    <row r="1291" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1291" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1291" s="12"/>
     </row>
-    <row r="1292" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1292" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1292" s="12"/>
     </row>
-    <row r="1293" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1293" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1293" s="12"/>
     </row>
-    <row r="1294" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1294" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1294" s="12"/>
     </row>
-    <row r="1295" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1295" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1295" s="12"/>
     </row>
-    <row r="1296" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1296" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1296" s="12"/>
     </row>
-    <row r="1297" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1297" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1297" s="12"/>
     </row>
-    <row r="1298" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1298" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1298" s="12"/>
     </row>
-    <row r="1299" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1299" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1299" s="12"/>
     </row>
-    <row r="1300" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1300" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1300" s="12"/>
     </row>
-    <row r="1301" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1301" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1301" s="12"/>
     </row>
-    <row r="1302" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1302" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1302" s="12"/>
     </row>
-    <row r="1303" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1303" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1303" s="12"/>
     </row>
-    <row r="1304" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1304" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1304" s="12"/>
     </row>
-    <row r="1305" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1305" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1305" s="12"/>
     </row>
-    <row r="1306" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1306" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1306" s="12"/>
     </row>
-    <row r="1307" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1307" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1307" s="12"/>
     </row>
-    <row r="1308" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1308" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1308" s="12"/>
     </row>
-    <row r="1309" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1309" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1309" s="12"/>
     </row>
-    <row r="1310" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1310" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1310" s="12"/>
     </row>
-    <row r="1311" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1311" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1311" s="12"/>
     </row>
-    <row r="1312" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1312" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1312" s="12"/>
     </row>
-    <row r="1313" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1313" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1313" s="12"/>
     </row>
-    <row r="1314" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1314" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1314" s="12"/>
     </row>
-    <row r="1315" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1315" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1315" s="12"/>
     </row>
-    <row r="1316" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1316" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1316" s="12"/>
     </row>
-    <row r="1317" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1317" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1317" s="12"/>
     </row>
-    <row r="1318" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1318" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1318" s="12"/>
     </row>
-    <row r="1319" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1319" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1319" s="12"/>
     </row>
-    <row r="1320" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1320" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1320" s="12"/>
     </row>
-    <row r="1321" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1321" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1321" s="12"/>
     </row>
-    <row r="1322" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1322" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1322" s="12"/>
     </row>
-    <row r="1323" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1323" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1323" s="12"/>
     </row>
-    <row r="1324" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1324" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1324" s="12"/>
     </row>
-    <row r="1325" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1325" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1325" s="12"/>
     </row>
-    <row r="1326" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1326" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1326" s="12"/>
     </row>
-    <row r="1327" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1327" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1327" s="12"/>
     </row>
-    <row r="1328" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1328" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1328" s="12"/>
     </row>
-    <row r="1329" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1329" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1329" s="12"/>
     </row>
-    <row r="1330" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1330" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1330" s="12"/>
     </row>
-    <row r="1331" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1331" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1331" s="12"/>
     </row>
-    <row r="1332" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1332" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1332" s="12"/>
     </row>
-    <row r="1333" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1333" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1333" s="12"/>
     </row>
-    <row r="1334" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1334" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1334" s="12"/>
     </row>
-    <row r="1335" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1335" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1335" s="12"/>
     </row>
-    <row r="1336" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1336" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1336" s="12"/>
     </row>
-    <row r="1337" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1337" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1337" s="12"/>
     </row>
-    <row r="1338" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1338" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1338" s="12"/>
     </row>
-    <row r="1339" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1339" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1339" s="12"/>
     </row>
-    <row r="1340" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1340" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1340" s="12"/>
     </row>
-    <row r="1341" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1341" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1341" s="12"/>
     </row>
-    <row r="1342" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1342" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1342" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2026:R1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2026:R1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>города</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Тип_доставки</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>список_температур</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>документы</formula1>
     </dataValidation>
   </dataValidations>
@@ -4861,7 +4862,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>'Списки (не трогать)'!$A$2:$A$7</xm:f>
           </x14:formula1>
@@ -4874,17 +4875,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="2" width="26.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.09765625" customWidth="1"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -4898,7 +4899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -4912,7 +4913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -4937,17 +4938,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -4959,40 +4960,40 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B3:N26"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.8984375" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.25" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>37</v>
       </c>
@@ -5007,13 +5008,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="K7" s="5"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>41</v>
       </c>
@@ -5021,7 +5022,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>42</v>
       </c>
@@ -5029,12 +5030,12 @@
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>43</v>
       </c>
@@ -5042,17 +5043,17 @@
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -5068,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>48</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>50</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>52</v>
       </c>
@@ -5092,7 +5093,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>53</v>
       </c>
@@ -5100,29 +5101,29 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>54</v>
       </c>
       <c r="D21" s="7">
         <f ca="1">TODAY()</f>
-        <v>45964</v>
+        <v>46092</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>61</v>
       </c>

--- a/blankimport.xlsx
+++ b/blankimport.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Golang projects\src\mstorefgo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grillman\go\warehouseHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ED1A00-6F15-4462-8A48-E21EF21DB2A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Импорт" sheetId="1" r:id="rId1"/>
@@ -23,7 +24,7 @@
     <definedName name="список_температур">'Списки (не трогать)'!$B$2:$B$4</definedName>
     <definedName name="Тип_доставки">'Списки (не трогать)'!$D$2:$D$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="330"/>
@@ -270,7 +271,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
@@ -674,35 +675,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y1342"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.3984375" customWidth="1"/>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="37.3984375" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="37.375" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="8" customWidth="1"/>
     <col min="5" max="5" width="130.5" customWidth="1"/>
-    <col min="6" max="8" width="15.3984375" customWidth="1"/>
-    <col min="9" max="9" width="166.69921875" customWidth="1"/>
-    <col min="10" max="10" width="25.3984375" customWidth="1"/>
+    <col min="6" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="166.75" customWidth="1"/>
+    <col min="10" max="10" width="25.375" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="22.09765625" customWidth="1"/>
+    <col min="14" max="14" width="22.125" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="26.19921875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="30.59765625" customWidth="1"/>
+    <col min="16" max="16" width="26.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.625" customWidth="1"/>
     <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="21.8984375" customWidth="1"/>
-    <col min="20" max="20" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.875" customWidth="1"/>
+    <col min="20" max="20" width="21.875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="1017" max="1019" width="8.3984375" customWidth="1"/>
+    <col min="23" max="23" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1017" max="1019" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -779,4080 +780,4080 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F2" s="10"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="P2" s="12"/>
       <c r="R2" s="12"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="P3" s="12"/>
       <c r="R3" s="12"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F4" s="10"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="P4" s="12"/>
       <c r="R4" s="12"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="P5" s="12"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="P6" s="12"/>
       <c r="R6" s="12"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="P7" s="12"/>
       <c r="R7" s="12"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="P8" s="12"/>
       <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="P9" s="12"/>
       <c r="R9" s="12"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="P10" s="12"/>
       <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="P11" s="12"/>
       <c r="R11" s="12"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="P12" s="12"/>
       <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R13" s="12"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R14" s="12"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R15" s="12"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R16" s="12"/>
     </row>
-    <row r="17" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R17" s="12"/>
     </row>
-    <row r="18" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R18" s="12"/>
     </row>
-    <row r="19" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R19" s="12"/>
     </row>
-    <row r="20" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R20" s="12"/>
     </row>
-    <row r="21" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R21" s="12"/>
     </row>
-    <row r="22" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R22" s="12"/>
     </row>
-    <row r="23" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R23" s="12"/>
     </row>
-    <row r="24" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R25" s="12"/>
     </row>
-    <row r="26" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R26" s="12"/>
     </row>
-    <row r="27" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R27" s="12"/>
     </row>
-    <row r="28" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R28" s="12"/>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R29" s="12"/>
     </row>
-    <row r="30" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R30" s="12"/>
     </row>
-    <row r="31" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R31" s="12"/>
     </row>
-    <row r="32" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R32" s="12"/>
     </row>
-    <row r="33" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R33" s="12"/>
     </row>
-    <row r="34" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R34" s="12"/>
     </row>
-    <row r="35" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R35" s="12"/>
     </row>
-    <row r="36" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R36" s="12"/>
     </row>
-    <row r="37" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R37" s="12"/>
     </row>
-    <row r="38" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R38" s="12"/>
     </row>
-    <row r="39" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R39" s="12"/>
     </row>
-    <row r="40" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R40" s="12"/>
     </row>
-    <row r="41" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R41" s="12"/>
     </row>
-    <row r="42" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R42" s="12"/>
     </row>
-    <row r="43" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R43" s="12"/>
     </row>
-    <row r="44" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R44" s="12"/>
     </row>
-    <row r="45" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R45" s="12"/>
     </row>
-    <row r="46" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R46" s="12"/>
     </row>
-    <row r="47" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R47" s="12"/>
     </row>
-    <row r="48" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R49" s="12"/>
     </row>
-    <row r="50" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R50" s="12"/>
     </row>
-    <row r="51" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R52" s="12"/>
     </row>
-    <row r="53" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R53" s="12"/>
     </row>
-    <row r="54" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R54" s="12"/>
     </row>
-    <row r="55" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R55" s="12"/>
     </row>
-    <row r="56" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R56" s="12"/>
     </row>
-    <row r="57" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R57" s="12"/>
     </row>
-    <row r="58" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R58" s="12"/>
     </row>
-    <row r="59" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R59" s="12"/>
     </row>
-    <row r="60" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R60" s="12"/>
     </row>
-    <row r="61" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R61" s="12"/>
     </row>
-    <row r="62" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R62" s="12"/>
     </row>
-    <row r="63" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R63" s="12"/>
     </row>
-    <row r="64" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R64" s="12"/>
     </row>
-    <row r="65" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R65" s="12"/>
     </row>
-    <row r="66" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R66" s="12"/>
     </row>
-    <row r="67" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R67" s="12"/>
     </row>
-    <row r="68" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R68" s="12"/>
     </row>
-    <row r="69" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R69" s="12"/>
     </row>
-    <row r="70" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R70" s="12"/>
     </row>
-    <row r="71" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R71" s="12"/>
     </row>
-    <row r="72" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R72" s="12"/>
     </row>
-    <row r="73" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R73" s="12"/>
     </row>
-    <row r="74" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R74" s="12"/>
     </row>
-    <row r="75" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R75" s="12"/>
     </row>
-    <row r="76" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R76" s="12"/>
     </row>
-    <row r="77" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R77" s="12"/>
     </row>
-    <row r="78" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R78" s="12"/>
     </row>
-    <row r="79" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R79" s="12"/>
     </row>
-    <row r="80" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R80" s="12"/>
     </row>
-    <row r="81" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R81" s="12"/>
     </row>
-    <row r="82" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R82" s="12"/>
     </row>
-    <row r="83" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R83" s="12"/>
     </row>
-    <row r="84" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R84" s="12"/>
     </row>
-    <row r="85" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R85" s="12"/>
     </row>
-    <row r="86" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R86" s="12"/>
     </row>
-    <row r="87" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R87" s="12"/>
     </row>
-    <row r="88" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R88" s="12"/>
     </row>
-    <row r="89" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R89" s="12"/>
     </row>
-    <row r="90" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R90" s="12"/>
     </row>
-    <row r="91" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R91" s="12"/>
     </row>
-    <row r="92" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R92" s="12"/>
     </row>
-    <row r="93" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R93" s="12"/>
     </row>
-    <row r="94" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R94" s="12"/>
     </row>
-    <row r="95" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R95" s="12"/>
     </row>
-    <row r="96" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R96" s="12"/>
     </row>
-    <row r="97" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R97" s="12"/>
     </row>
-    <row r="98" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R98" s="12"/>
     </row>
-    <row r="99" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R99" s="12"/>
     </row>
-    <row r="100" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R100" s="12"/>
     </row>
-    <row r="101" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R101" s="12"/>
     </row>
-    <row r="102" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R102" s="12"/>
     </row>
-    <row r="103" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R103" s="12"/>
     </row>
-    <row r="104" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R104" s="12"/>
     </row>
-    <row r="105" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R105" s="12"/>
     </row>
-    <row r="106" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R106" s="12"/>
     </row>
-    <row r="107" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R107" s="12"/>
     </row>
-    <row r="108" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R108" s="12"/>
     </row>
-    <row r="109" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R109" s="12"/>
     </row>
-    <row r="110" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R110" s="12"/>
     </row>
-    <row r="111" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R111" s="12"/>
     </row>
-    <row r="112" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R112" s="12"/>
     </row>
-    <row r="113" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R113" s="12"/>
     </row>
-    <row r="114" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R114" s="12"/>
     </row>
-    <row r="115" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R115" s="12"/>
     </row>
-    <row r="116" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R116" s="12"/>
     </row>
-    <row r="117" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R117" s="12"/>
     </row>
-    <row r="118" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R118" s="12"/>
     </row>
-    <row r="119" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R119" s="12"/>
     </row>
-    <row r="120" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R120" s="12"/>
     </row>
-    <row r="121" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R121" s="12"/>
     </row>
-    <row r="122" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R122" s="12"/>
     </row>
-    <row r="123" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R123" s="12"/>
     </row>
-    <row r="124" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R124" s="12"/>
     </row>
-    <row r="125" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R125" s="12"/>
     </row>
-    <row r="126" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R126" s="12"/>
     </row>
-    <row r="127" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R127" s="12"/>
     </row>
-    <row r="128" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R128" s="12"/>
     </row>
-    <row r="129" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R129" s="12"/>
     </row>
-    <row r="130" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R130" s="12"/>
     </row>
-    <row r="131" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R131" s="12"/>
     </row>
-    <row r="132" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R132" s="12"/>
     </row>
-    <row r="133" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R133" s="12"/>
     </row>
-    <row r="134" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R134" s="12"/>
     </row>
-    <row r="135" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R135" s="12"/>
     </row>
-    <row r="136" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R136" s="12"/>
     </row>
-    <row r="137" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R137" s="12"/>
     </row>
-    <row r="138" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R138" s="12"/>
     </row>
-    <row r="139" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R139" s="12"/>
     </row>
-    <row r="140" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R140" s="12"/>
     </row>
-    <row r="141" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R141" s="12"/>
     </row>
-    <row r="142" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R142" s="12"/>
     </row>
-    <row r="143" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R143" s="12"/>
     </row>
-    <row r="144" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R144" s="12"/>
     </row>
-    <row r="145" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R145" s="12"/>
     </row>
-    <row r="146" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R146" s="12"/>
     </row>
-    <row r="147" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R147" s="12"/>
     </row>
-    <row r="148" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R148" s="12"/>
     </row>
-    <row r="149" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R149" s="12"/>
     </row>
-    <row r="150" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R150" s="12"/>
     </row>
-    <row r="151" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R151" s="12"/>
     </row>
-    <row r="152" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R152" s="12"/>
     </row>
-    <row r="153" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R153" s="12"/>
     </row>
-    <row r="154" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R154" s="12"/>
     </row>
-    <row r="155" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R155" s="12"/>
     </row>
-    <row r="156" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R156" s="12"/>
     </row>
-    <row r="157" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R157" s="12"/>
     </row>
-    <row r="158" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R158" s="12"/>
     </row>
-    <row r="159" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R159" s="12"/>
     </row>
-    <row r="160" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R160" s="12"/>
     </row>
-    <row r="161" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R161" s="12"/>
     </row>
-    <row r="162" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R162" s="12"/>
     </row>
-    <row r="163" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R163" s="12"/>
     </row>
-    <row r="164" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R164" s="12"/>
     </row>
-    <row r="165" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R165" s="12"/>
     </row>
-    <row r="166" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R166" s="12"/>
     </row>
-    <row r="167" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R167" s="12"/>
     </row>
-    <row r="168" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R168" s="12"/>
     </row>
-    <row r="169" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R169" s="12"/>
     </row>
-    <row r="170" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R170" s="12"/>
     </row>
-    <row r="171" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R171" s="12"/>
     </row>
-    <row r="172" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R172" s="12"/>
     </row>
-    <row r="173" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R173" s="12"/>
     </row>
-    <row r="174" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R174" s="12"/>
     </row>
-    <row r="175" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R175" s="12"/>
     </row>
-    <row r="176" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R176" s="12"/>
     </row>
-    <row r="177" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R177" s="12"/>
     </row>
-    <row r="178" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R178" s="12"/>
     </row>
-    <row r="179" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R179" s="12"/>
     </row>
-    <row r="180" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R180" s="12"/>
     </row>
-    <row r="181" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R181" s="12"/>
     </row>
-    <row r="182" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R182" s="12"/>
     </row>
-    <row r="183" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R183" s="12"/>
     </row>
-    <row r="184" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R184" s="12"/>
     </row>
-    <row r="185" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R185" s="12"/>
     </row>
-    <row r="186" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R186" s="12"/>
     </row>
-    <row r="187" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R187" s="12"/>
     </row>
-    <row r="188" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R188" s="12"/>
     </row>
-    <row r="189" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R189" s="12"/>
     </row>
-    <row r="190" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R190" s="12"/>
     </row>
-    <row r="191" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R191" s="12"/>
     </row>
-    <row r="192" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R192" s="12"/>
     </row>
-    <row r="193" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R193" s="12"/>
     </row>
-    <row r="194" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R194" s="12"/>
     </row>
-    <row r="195" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R195" s="12"/>
     </row>
-    <row r="196" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R196" s="12"/>
     </row>
-    <row r="197" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R197" s="12"/>
     </row>
-    <row r="198" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R198" s="12"/>
     </row>
-    <row r="199" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R199" s="12"/>
     </row>
-    <row r="200" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R200" s="12"/>
     </row>
-    <row r="201" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R201" s="12"/>
     </row>
-    <row r="202" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R202" s="12"/>
     </row>
-    <row r="203" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R203" s="12"/>
     </row>
-    <row r="204" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R204" s="12"/>
     </row>
-    <row r="205" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R205" s="12"/>
     </row>
-    <row r="206" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R206" s="12"/>
     </row>
-    <row r="207" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R207" s="12"/>
     </row>
-    <row r="208" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R208" s="12"/>
     </row>
-    <row r="209" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R209" s="12"/>
     </row>
-    <row r="210" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R210" s="12"/>
     </row>
-    <row r="211" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R211" s="12"/>
     </row>
-    <row r="212" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R212" s="12"/>
     </row>
-    <row r="213" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R213" s="12"/>
     </row>
-    <row r="214" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R214" s="12"/>
     </row>
-    <row r="215" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R215" s="12"/>
     </row>
-    <row r="216" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R216" s="12"/>
     </row>
-    <row r="217" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R217" s="12"/>
     </row>
-    <row r="218" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R218" s="12"/>
     </row>
-    <row r="219" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R219" s="12"/>
     </row>
-    <row r="220" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R220" s="12"/>
     </row>
-    <row r="221" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R221" s="12"/>
     </row>
-    <row r="222" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R222" s="12"/>
     </row>
-    <row r="223" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R223" s="12"/>
     </row>
-    <row r="224" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R224" s="12"/>
     </row>
-    <row r="225" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R225" s="12"/>
     </row>
-    <row r="226" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R226" s="12"/>
     </row>
-    <row r="227" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R227" s="12"/>
     </row>
-    <row r="228" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R228" s="12"/>
     </row>
-    <row r="229" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R229" s="12"/>
     </row>
-    <row r="230" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R230" s="12"/>
     </row>
-    <row r="231" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R231" s="12"/>
     </row>
-    <row r="232" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R232" s="12"/>
     </row>
-    <row r="233" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R233" s="12"/>
     </row>
-    <row r="234" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R234" s="12"/>
     </row>
-    <row r="235" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R235" s="12"/>
     </row>
-    <row r="236" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R236" s="12"/>
     </row>
-    <row r="237" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R237" s="12"/>
     </row>
-    <row r="238" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R238" s="12"/>
     </row>
-    <row r="239" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R239" s="12"/>
     </row>
-    <row r="240" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R240" s="12"/>
     </row>
-    <row r="241" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R241" s="12"/>
     </row>
-    <row r="242" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R242" s="12"/>
     </row>
-    <row r="243" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R243" s="12"/>
     </row>
-    <row r="244" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R244" s="12"/>
     </row>
-    <row r="245" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R245" s="12"/>
     </row>
-    <row r="246" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R246" s="12"/>
     </row>
-    <row r="247" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R247" s="12"/>
     </row>
-    <row r="248" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R248" s="12"/>
     </row>
-    <row r="249" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R249" s="12"/>
     </row>
-    <row r="250" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R250" s="12"/>
     </row>
-    <row r="251" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R251" s="12"/>
     </row>
-    <row r="252" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R252" s="12"/>
     </row>
-    <row r="253" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R253" s="12"/>
     </row>
-    <row r="254" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R254" s="12"/>
     </row>
-    <row r="255" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R255" s="12"/>
     </row>
-    <row r="256" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R256" s="12"/>
     </row>
-    <row r="257" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R257" s="12"/>
     </row>
-    <row r="258" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R258" s="12"/>
     </row>
-    <row r="259" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R259" s="12"/>
     </row>
-    <row r="260" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R260" s="12"/>
     </row>
-    <row r="261" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R261" s="12"/>
     </row>
-    <row r="262" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R262" s="12"/>
     </row>
-    <row r="263" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R263" s="12"/>
     </row>
-    <row r="264" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R264" s="12"/>
     </row>
-    <row r="265" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R265" s="12"/>
     </row>
-    <row r="266" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R266" s="12"/>
     </row>
-    <row r="267" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R267" s="12"/>
     </row>
-    <row r="268" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R268" s="12"/>
     </row>
-    <row r="269" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R269" s="12"/>
     </row>
-    <row r="270" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R270" s="12"/>
     </row>
-    <row r="271" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R271" s="12"/>
     </row>
-    <row r="272" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R272" s="12"/>
     </row>
-    <row r="273" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R273" s="12"/>
     </row>
-    <row r="274" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R274" s="12"/>
     </row>
-    <row r="275" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R275" s="12"/>
     </row>
-    <row r="276" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="276" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R276" s="12"/>
     </row>
-    <row r="277" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R277" s="12"/>
     </row>
-    <row r="278" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R278" s="12"/>
     </row>
-    <row r="279" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R279" s="12"/>
     </row>
-    <row r="280" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R280" s="12"/>
     </row>
-    <row r="281" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R281" s="12"/>
     </row>
-    <row r="282" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R282" s="12"/>
     </row>
-    <row r="283" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R283" s="12"/>
     </row>
-    <row r="284" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R284" s="12"/>
     </row>
-    <row r="285" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="285" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R285" s="12"/>
     </row>
-    <row r="286" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R286" s="12"/>
     </row>
-    <row r="287" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R287" s="12"/>
     </row>
-    <row r="288" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R288" s="12"/>
     </row>
-    <row r="289" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="289" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R289" s="12"/>
     </row>
-    <row r="290" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R290" s="12"/>
     </row>
-    <row r="291" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R291" s="12"/>
     </row>
-    <row r="292" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R292" s="12"/>
     </row>
-    <row r="293" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R293" s="12"/>
     </row>
-    <row r="294" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R294" s="12"/>
     </row>
-    <row r="295" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R295" s="12"/>
     </row>
-    <row r="296" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R296" s="12"/>
     </row>
-    <row r="297" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R297" s="12"/>
     </row>
-    <row r="298" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R298" s="12"/>
     </row>
-    <row r="299" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R299" s="12"/>
     </row>
-    <row r="300" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R300" s="12"/>
     </row>
-    <row r="301" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R301" s="12"/>
     </row>
-    <row r="302" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="302" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R302" s="12"/>
     </row>
-    <row r="303" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R303" s="12"/>
     </row>
-    <row r="304" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="304" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R304" s="12"/>
     </row>
-    <row r="305" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R305" s="12"/>
     </row>
-    <row r="306" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R306" s="12"/>
     </row>
-    <row r="307" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R307" s="12"/>
     </row>
-    <row r="308" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R308" s="12"/>
     </row>
-    <row r="309" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R309" s="12"/>
     </row>
-    <row r="310" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R310" s="12"/>
     </row>
-    <row r="311" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R311" s="12"/>
     </row>
-    <row r="312" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R312" s="12"/>
     </row>
-    <row r="313" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R313" s="12"/>
     </row>
-    <row r="314" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R314" s="12"/>
     </row>
-    <row r="315" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="315" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R315" s="12"/>
     </row>
-    <row r="316" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R316" s="12"/>
     </row>
-    <row r="317" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R317" s="12"/>
     </row>
-    <row r="318" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R318" s="12"/>
     </row>
-    <row r="319" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R319" s="12"/>
     </row>
-    <row r="320" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R320" s="12"/>
     </row>
-    <row r="321" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R321" s="12"/>
     </row>
-    <row r="322" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R322" s="12"/>
     </row>
-    <row r="323" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R323" s="12"/>
     </row>
-    <row r="324" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R324" s="12"/>
     </row>
-    <row r="325" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R325" s="12"/>
     </row>
-    <row r="326" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R326" s="12"/>
     </row>
-    <row r="327" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R327" s="12"/>
     </row>
-    <row r="328" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R328" s="12"/>
     </row>
-    <row r="329" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R329" s="12"/>
     </row>
-    <row r="330" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R330" s="12"/>
     </row>
-    <row r="331" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R331" s="12"/>
     </row>
-    <row r="332" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R332" s="12"/>
     </row>
-    <row r="333" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R333" s="12"/>
     </row>
-    <row r="334" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R334" s="12"/>
     </row>
-    <row r="335" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R335" s="12"/>
     </row>
-    <row r="336" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R336" s="12"/>
     </row>
-    <row r="337" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R337" s="12"/>
     </row>
-    <row r="338" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R338" s="12"/>
     </row>
-    <row r="339" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R339" s="12"/>
     </row>
-    <row r="340" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="340" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R340" s="12"/>
     </row>
-    <row r="341" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R341" s="12"/>
     </row>
-    <row r="342" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="342" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R342" s="12"/>
     </row>
-    <row r="343" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R343" s="12"/>
     </row>
-    <row r="344" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R344" s="12"/>
     </row>
-    <row r="345" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R345" s="12"/>
     </row>
-    <row r="346" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R346" s="12"/>
     </row>
-    <row r="347" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R347" s="12"/>
     </row>
-    <row r="348" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R348" s="12"/>
     </row>
-    <row r="349" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R349" s="12"/>
     </row>
-    <row r="350" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R350" s="12"/>
     </row>
-    <row r="351" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R351" s="12"/>
     </row>
-    <row r="352" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R352" s="12"/>
     </row>
-    <row r="353" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R353" s="12"/>
     </row>
-    <row r="354" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R354" s="12"/>
     </row>
-    <row r="355" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R355" s="12"/>
     </row>
-    <row r="356" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R356" s="12"/>
     </row>
-    <row r="357" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R357" s="12"/>
     </row>
-    <row r="358" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R358" s="12"/>
     </row>
-    <row r="359" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R359" s="12"/>
     </row>
-    <row r="360" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R360" s="12"/>
     </row>
-    <row r="361" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R361" s="12"/>
     </row>
-    <row r="362" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R362" s="12"/>
     </row>
-    <row r="363" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R363" s="12"/>
     </row>
-    <row r="364" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="364" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R364" s="12"/>
     </row>
-    <row r="365" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="365" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R365" s="12"/>
     </row>
-    <row r="366" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="366" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R366" s="12"/>
     </row>
-    <row r="367" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="367" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R367" s="12"/>
     </row>
-    <row r="368" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="368" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R368" s="12"/>
     </row>
-    <row r="369" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R369" s="12"/>
     </row>
-    <row r="370" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R370" s="12"/>
     </row>
-    <row r="371" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R371" s="12"/>
     </row>
-    <row r="372" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R372" s="12"/>
     </row>
-    <row r="373" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R373" s="12"/>
     </row>
-    <row r="374" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R374" s="12"/>
     </row>
-    <row r="375" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R375" s="12"/>
     </row>
-    <row r="376" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R376" s="12"/>
     </row>
-    <row r="377" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R377" s="12"/>
     </row>
-    <row r="378" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R378" s="12"/>
     </row>
-    <row r="379" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R379" s="12"/>
     </row>
-    <row r="380" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R380" s="12"/>
     </row>
-    <row r="381" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="381" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R381" s="12"/>
     </row>
-    <row r="382" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="382" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R382" s="12"/>
     </row>
-    <row r="383" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R383" s="12"/>
     </row>
-    <row r="384" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R384" s="12"/>
     </row>
-    <row r="385" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R385" s="12"/>
     </row>
-    <row r="386" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R386" s="12"/>
     </row>
-    <row r="387" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R387" s="12"/>
     </row>
-    <row r="388" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R388" s="12"/>
     </row>
-    <row r="389" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="389" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R389" s="12"/>
     </row>
-    <row r="390" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="390" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R390" s="12"/>
     </row>
-    <row r="391" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="391" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R391" s="12"/>
     </row>
-    <row r="392" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="392" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R392" s="12"/>
     </row>
-    <row r="393" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="393" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R393" s="12"/>
     </row>
-    <row r="394" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="394" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R394" s="12"/>
     </row>
-    <row r="395" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="395" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R395" s="12"/>
     </row>
-    <row r="396" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="396" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R396" s="12"/>
     </row>
-    <row r="397" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="397" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R397" s="12"/>
     </row>
-    <row r="398" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="398" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R398" s="12"/>
     </row>
-    <row r="399" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="399" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R399" s="12"/>
     </row>
-    <row r="400" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="400" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R400" s="12"/>
     </row>
-    <row r="401" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="401" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R401" s="12"/>
     </row>
-    <row r="402" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="402" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R402" s="12"/>
     </row>
-    <row r="403" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="403" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R403" s="12"/>
     </row>
-    <row r="404" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="404" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R404" s="12"/>
     </row>
-    <row r="405" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="405" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R405" s="12"/>
     </row>
-    <row r="406" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="406" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R406" s="12"/>
     </row>
-    <row r="407" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="407" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R407" s="12"/>
     </row>
-    <row r="408" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="408" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R408" s="12"/>
     </row>
-    <row r="409" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="409" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R409" s="12"/>
     </row>
-    <row r="410" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="410" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R410" s="12"/>
     </row>
-    <row r="411" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="411" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R411" s="12"/>
     </row>
-    <row r="412" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="412" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R412" s="12"/>
     </row>
-    <row r="413" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="413" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R413" s="12"/>
     </row>
-    <row r="414" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="414" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R414" s="12"/>
     </row>
-    <row r="415" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="415" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R415" s="12"/>
     </row>
-    <row r="416" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="416" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R416" s="12"/>
     </row>
-    <row r="417" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="417" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R417" s="12"/>
     </row>
-    <row r="418" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="418" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R418" s="12"/>
     </row>
-    <row r="419" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="419" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R419" s="12"/>
     </row>
-    <row r="420" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="420" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R420" s="12"/>
     </row>
-    <row r="421" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="421" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R421" s="12"/>
     </row>
-    <row r="422" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="422" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R422" s="12"/>
     </row>
-    <row r="423" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="423" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R423" s="12"/>
     </row>
-    <row r="424" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="424" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R424" s="12"/>
     </row>
-    <row r="425" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="425" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R425" s="12"/>
     </row>
-    <row r="426" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="426" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R426" s="12"/>
     </row>
-    <row r="427" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="427" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R427" s="12"/>
     </row>
-    <row r="428" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="428" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R428" s="12"/>
     </row>
-    <row r="429" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="429" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R429" s="12"/>
     </row>
-    <row r="430" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="430" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R430" s="12"/>
     </row>
-    <row r="431" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="431" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R431" s="12"/>
     </row>
-    <row r="432" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="432" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R432" s="12"/>
     </row>
-    <row r="433" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="433" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R433" s="12"/>
     </row>
-    <row r="434" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="434" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R434" s="12"/>
     </row>
-    <row r="435" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="435" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R435" s="12"/>
     </row>
-    <row r="436" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="436" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R436" s="12"/>
     </row>
-    <row r="437" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="437" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R437" s="12"/>
     </row>
-    <row r="438" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="438" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R438" s="12"/>
     </row>
-    <row r="439" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="439" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R439" s="12"/>
     </row>
-    <row r="440" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="440" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R440" s="12"/>
     </row>
-    <row r="441" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="441" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R441" s="12"/>
     </row>
-    <row r="442" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="442" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R442" s="12"/>
     </row>
-    <row r="443" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="443" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R443" s="12"/>
     </row>
-    <row r="444" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="444" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R444" s="12"/>
     </row>
-    <row r="445" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="445" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R445" s="12"/>
     </row>
-    <row r="446" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="446" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R446" s="12"/>
     </row>
-    <row r="447" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="447" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R447" s="12"/>
     </row>
-    <row r="448" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="448" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R448" s="12"/>
     </row>
-    <row r="449" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="449" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R449" s="12"/>
     </row>
-    <row r="450" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="450" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R450" s="12"/>
     </row>
-    <row r="451" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="451" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R451" s="12"/>
     </row>
-    <row r="452" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="452" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R452" s="12"/>
     </row>
-    <row r="453" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="453" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R453" s="12"/>
     </row>
-    <row r="454" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="454" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R454" s="12"/>
     </row>
-    <row r="455" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="455" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R455" s="12"/>
     </row>
-    <row r="456" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="456" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R456" s="12"/>
     </row>
-    <row r="457" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="457" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R457" s="12"/>
     </row>
-    <row r="458" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="458" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R458" s="12"/>
     </row>
-    <row r="459" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="459" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R459" s="12"/>
     </row>
-    <row r="460" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="460" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R460" s="12"/>
     </row>
-    <row r="461" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="461" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R461" s="12"/>
     </row>
-    <row r="462" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="462" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R462" s="12"/>
     </row>
-    <row r="463" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="463" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R463" s="12"/>
     </row>
-    <row r="464" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="464" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R464" s="12"/>
     </row>
-    <row r="465" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="465" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R465" s="12"/>
     </row>
-    <row r="466" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="466" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R466" s="12"/>
     </row>
-    <row r="467" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="467" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R467" s="12"/>
     </row>
-    <row r="468" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="468" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R468" s="12"/>
     </row>
-    <row r="469" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="469" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R469" s="12"/>
     </row>
-    <row r="470" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="470" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R470" s="12"/>
     </row>
-    <row r="471" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="471" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R471" s="12"/>
     </row>
-    <row r="472" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="472" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R472" s="12"/>
     </row>
-    <row r="473" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="473" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R473" s="12"/>
     </row>
-    <row r="474" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="474" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R474" s="12"/>
     </row>
-    <row r="475" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="475" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R475" s="12"/>
     </row>
-    <row r="476" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="476" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R476" s="12"/>
     </row>
-    <row r="477" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="477" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R477" s="12"/>
     </row>
-    <row r="478" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="478" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R478" s="12"/>
     </row>
-    <row r="479" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="479" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R479" s="12"/>
     </row>
-    <row r="480" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="480" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R480" s="12"/>
     </row>
-    <row r="481" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="481" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R481" s="12"/>
     </row>
-    <row r="482" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="482" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R482" s="12"/>
     </row>
-    <row r="483" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="483" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R483" s="12"/>
     </row>
-    <row r="484" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="484" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R484" s="12"/>
     </row>
-    <row r="485" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="485" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R485" s="12"/>
     </row>
-    <row r="486" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="486" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R486" s="12"/>
     </row>
-    <row r="487" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="487" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R487" s="12"/>
     </row>
-    <row r="488" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="488" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R488" s="12"/>
     </row>
-    <row r="489" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="489" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R489" s="12"/>
     </row>
-    <row r="490" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="490" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R490" s="12"/>
     </row>
-    <row r="491" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="491" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R491" s="12"/>
     </row>
-    <row r="492" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="492" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R492" s="12"/>
     </row>
-    <row r="493" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="493" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R493" s="12"/>
     </row>
-    <row r="494" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="494" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R494" s="12"/>
     </row>
-    <row r="495" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="495" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R495" s="12"/>
     </row>
-    <row r="496" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="496" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R496" s="12"/>
     </row>
-    <row r="497" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="497" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R497" s="12"/>
     </row>
-    <row r="498" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="498" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R498" s="12"/>
     </row>
-    <row r="499" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="499" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R499" s="12"/>
     </row>
-    <row r="500" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="500" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R500" s="12"/>
     </row>
-    <row r="501" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="501" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R501" s="12"/>
     </row>
-    <row r="502" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="502" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R502" s="12"/>
     </row>
-    <row r="503" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="503" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R503" s="12"/>
     </row>
-    <row r="504" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="504" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R504" s="12"/>
     </row>
-    <row r="505" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="505" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R505" s="12"/>
     </row>
-    <row r="506" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="506" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R506" s="12"/>
     </row>
-    <row r="507" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="507" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R507" s="12"/>
     </row>
-    <row r="508" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="508" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R508" s="12"/>
     </row>
-    <row r="509" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="509" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R509" s="12"/>
     </row>
-    <row r="510" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="510" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R510" s="12"/>
     </row>
-    <row r="511" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="511" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R511" s="12"/>
     </row>
-    <row r="512" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="512" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R512" s="12"/>
     </row>
-    <row r="513" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="513" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R513" s="12"/>
     </row>
-    <row r="514" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="514" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R514" s="12"/>
     </row>
-    <row r="515" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="515" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R515" s="12"/>
     </row>
-    <row r="516" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="516" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R516" s="12"/>
     </row>
-    <row r="517" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="517" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R517" s="12"/>
     </row>
-    <row r="518" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="518" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R518" s="12"/>
     </row>
-    <row r="519" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="519" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R519" s="12"/>
     </row>
-    <row r="520" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="520" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R520" s="12"/>
     </row>
-    <row r="521" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="521" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R521" s="12"/>
     </row>
-    <row r="522" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="522" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R522" s="12"/>
     </row>
-    <row r="523" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="523" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R523" s="12"/>
     </row>
-    <row r="524" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="524" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R524" s="12"/>
     </row>
-    <row r="525" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="525" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R525" s="12"/>
     </row>
-    <row r="526" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="526" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R526" s="12"/>
     </row>
-    <row r="527" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="527" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R527" s="12"/>
     </row>
-    <row r="528" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="528" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R528" s="12"/>
     </row>
-    <row r="529" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="529" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R529" s="12"/>
     </row>
-    <row r="530" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="530" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R530" s="12"/>
     </row>
-    <row r="531" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="531" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R531" s="12"/>
     </row>
-    <row r="532" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="532" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R532" s="12"/>
     </row>
-    <row r="533" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="533" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R533" s="12"/>
     </row>
-    <row r="534" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="534" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R534" s="12"/>
     </row>
-    <row r="535" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="535" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R535" s="12"/>
     </row>
-    <row r="536" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="536" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R536" s="12"/>
     </row>
-    <row r="537" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="537" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R537" s="12"/>
     </row>
-    <row r="538" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="538" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R538" s="12"/>
     </row>
-    <row r="539" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="539" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R539" s="12"/>
     </row>
-    <row r="540" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="540" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R540" s="12"/>
     </row>
-    <row r="541" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="541" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R541" s="12"/>
     </row>
-    <row r="542" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="542" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R542" s="12"/>
     </row>
-    <row r="543" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="543" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R543" s="12"/>
     </row>
-    <row r="544" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="544" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R544" s="12"/>
     </row>
-    <row r="545" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="545" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R545" s="12"/>
     </row>
-    <row r="546" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="546" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R546" s="12"/>
     </row>
-    <row r="547" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="547" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R547" s="12"/>
     </row>
-    <row r="548" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="548" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R548" s="12"/>
     </row>
-    <row r="549" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="549" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R549" s="12"/>
     </row>
-    <row r="550" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="550" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R550" s="12"/>
     </row>
-    <row r="551" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="551" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R551" s="12"/>
     </row>
-    <row r="552" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="552" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R552" s="12"/>
     </row>
-    <row r="553" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="553" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R553" s="12"/>
     </row>
-    <row r="554" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="554" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R554" s="12"/>
     </row>
-    <row r="555" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="555" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R555" s="12"/>
     </row>
-    <row r="556" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="556" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R556" s="12"/>
     </row>
-    <row r="557" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="557" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R557" s="12"/>
     </row>
-    <row r="558" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="558" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R558" s="12"/>
     </row>
-    <row r="559" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="559" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R559" s="12"/>
     </row>
-    <row r="560" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="560" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R560" s="12"/>
     </row>
-    <row r="561" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="561" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R561" s="12"/>
     </row>
-    <row r="562" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="562" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R562" s="12"/>
     </row>
-    <row r="563" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="563" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R563" s="12"/>
     </row>
-    <row r="564" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="564" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R564" s="12"/>
     </row>
-    <row r="565" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="565" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R565" s="12"/>
     </row>
-    <row r="566" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="566" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R566" s="12"/>
     </row>
-    <row r="567" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="567" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R567" s="12"/>
     </row>
-    <row r="568" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="568" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R568" s="12"/>
     </row>
-    <row r="569" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="569" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R569" s="12"/>
     </row>
-    <row r="570" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="570" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R570" s="12"/>
     </row>
-    <row r="571" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="571" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R571" s="12"/>
     </row>
-    <row r="572" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="572" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R572" s="12"/>
     </row>
-    <row r="573" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="573" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R573" s="12"/>
     </row>
-    <row r="574" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="574" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R574" s="12"/>
     </row>
-    <row r="575" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="575" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R575" s="12"/>
     </row>
-    <row r="576" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="576" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R576" s="12"/>
     </row>
-    <row r="577" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="577" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R577" s="12"/>
     </row>
-    <row r="578" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="578" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R578" s="12"/>
     </row>
-    <row r="579" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="579" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R579" s="12"/>
     </row>
-    <row r="580" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="580" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R580" s="12"/>
     </row>
-    <row r="581" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="581" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R581" s="12"/>
     </row>
-    <row r="582" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="582" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R582" s="12"/>
     </row>
-    <row r="583" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="583" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R583" s="12"/>
     </row>
-    <row r="584" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="584" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R584" s="12"/>
     </row>
-    <row r="585" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="585" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R585" s="12"/>
     </row>
-    <row r="586" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="586" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R586" s="12"/>
     </row>
-    <row r="587" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="587" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R587" s="12"/>
     </row>
-    <row r="588" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="588" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R588" s="12"/>
     </row>
-    <row r="589" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="589" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R589" s="12"/>
     </row>
-    <row r="590" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="590" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R590" s="12"/>
     </row>
-    <row r="591" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="591" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R591" s="12"/>
     </row>
-    <row r="592" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="592" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R592" s="12"/>
     </row>
-    <row r="593" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="593" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R593" s="12"/>
     </row>
-    <row r="594" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="594" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R594" s="12"/>
     </row>
-    <row r="595" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="595" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R595" s="12"/>
     </row>
-    <row r="596" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="596" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R596" s="12"/>
     </row>
-    <row r="597" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="597" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R597" s="12"/>
     </row>
-    <row r="598" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="598" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R598" s="12"/>
     </row>
-    <row r="599" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="599" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R599" s="12"/>
     </row>
-    <row r="600" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="600" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R600" s="12"/>
     </row>
-    <row r="601" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="601" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R601" s="12"/>
     </row>
-    <row r="602" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="602" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R602" s="12"/>
     </row>
-    <row r="603" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="603" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R603" s="12"/>
     </row>
-    <row r="604" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="604" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R604" s="12"/>
     </row>
-    <row r="605" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="605" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R605" s="12"/>
     </row>
-    <row r="606" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="606" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R606" s="12"/>
     </row>
-    <row r="607" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="607" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R607" s="12"/>
     </row>
-    <row r="608" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="608" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R608" s="12"/>
     </row>
-    <row r="609" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="609" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R609" s="12"/>
     </row>
-    <row r="610" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="610" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R610" s="12"/>
     </row>
-    <row r="611" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="611" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R611" s="12"/>
     </row>
-    <row r="612" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="612" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R612" s="12"/>
     </row>
-    <row r="613" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="613" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R613" s="12"/>
     </row>
-    <row r="614" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="614" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R614" s="12"/>
     </row>
-    <row r="615" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="615" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R615" s="12"/>
     </row>
-    <row r="616" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="616" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R616" s="12"/>
     </row>
-    <row r="617" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="617" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R617" s="12"/>
     </row>
-    <row r="618" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="618" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R618" s="12"/>
     </row>
-    <row r="619" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="619" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R619" s="12"/>
     </row>
-    <row r="620" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="620" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R620" s="12"/>
     </row>
-    <row r="621" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="621" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R621" s="12"/>
     </row>
-    <row r="622" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="622" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R622" s="12"/>
     </row>
-    <row r="623" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="623" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R623" s="12"/>
     </row>
-    <row r="624" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="624" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R624" s="12"/>
     </row>
-    <row r="625" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="625" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R625" s="12"/>
     </row>
-    <row r="626" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="626" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R626" s="12"/>
     </row>
-    <row r="627" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="627" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R627" s="12"/>
     </row>
-    <row r="628" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="628" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R628" s="12"/>
     </row>
-    <row r="629" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="629" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R629" s="12"/>
     </row>
-    <row r="630" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="630" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R630" s="12"/>
     </row>
-    <row r="631" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="631" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R631" s="12"/>
     </row>
-    <row r="632" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="632" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R632" s="12"/>
     </row>
-    <row r="633" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="633" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R633" s="12"/>
     </row>
-    <row r="634" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="634" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R634" s="12"/>
     </row>
-    <row r="635" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="635" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R635" s="12"/>
     </row>
-    <row r="636" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="636" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R636" s="12"/>
     </row>
-    <row r="637" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="637" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R637" s="12"/>
     </row>
-    <row r="638" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="638" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R638" s="12"/>
     </row>
-    <row r="639" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="639" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R639" s="12"/>
     </row>
-    <row r="640" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="640" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R640" s="12"/>
     </row>
-    <row r="641" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="641" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R641" s="12"/>
     </row>
-    <row r="642" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="642" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R642" s="12"/>
     </row>
-    <row r="643" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="643" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R643" s="12"/>
     </row>
-    <row r="644" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="644" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R644" s="12"/>
     </row>
-    <row r="645" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="645" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R645" s="12"/>
     </row>
-    <row r="646" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="646" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R646" s="12"/>
     </row>
-    <row r="647" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="647" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R647" s="12"/>
     </row>
-    <row r="648" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="648" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R648" s="12"/>
     </row>
-    <row r="649" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="649" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R649" s="12"/>
     </row>
-    <row r="650" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="650" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R650" s="12"/>
     </row>
-    <row r="651" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="651" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R651" s="12"/>
     </row>
-    <row r="652" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="652" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R652" s="12"/>
     </row>
-    <row r="653" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="653" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R653" s="12"/>
     </row>
-    <row r="654" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="654" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R654" s="12"/>
     </row>
-    <row r="655" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="655" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R655" s="12"/>
     </row>
-    <row r="656" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="656" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R656" s="12"/>
     </row>
-    <row r="657" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="657" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R657" s="12"/>
     </row>
-    <row r="658" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="658" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R658" s="12"/>
     </row>
-    <row r="659" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="659" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R659" s="12"/>
     </row>
-    <row r="660" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="660" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R660" s="12"/>
     </row>
-    <row r="661" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="661" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R661" s="12"/>
     </row>
-    <row r="662" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="662" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R662" s="12"/>
     </row>
-    <row r="663" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="663" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R663" s="12"/>
     </row>
-    <row r="664" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="664" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R664" s="12"/>
     </row>
-    <row r="665" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="665" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R665" s="12"/>
     </row>
-    <row r="666" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="666" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R666" s="12"/>
     </row>
-    <row r="667" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="667" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R667" s="12"/>
     </row>
-    <row r="668" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="668" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R668" s="12"/>
     </row>
-    <row r="669" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="669" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R669" s="12"/>
     </row>
-    <row r="670" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="670" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R670" s="12"/>
     </row>
-    <row r="671" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="671" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R671" s="12"/>
     </row>
-    <row r="672" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="672" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R672" s="12"/>
     </row>
-    <row r="673" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="673" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R673" s="12"/>
     </row>
-    <row r="674" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="674" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R674" s="12"/>
     </row>
-    <row r="675" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="675" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R675" s="12"/>
     </row>
-    <row r="676" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="676" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R676" s="12"/>
     </row>
-    <row r="677" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="677" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R677" s="12"/>
     </row>
-    <row r="678" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="678" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R678" s="12"/>
     </row>
-    <row r="679" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="679" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R679" s="12"/>
     </row>
-    <row r="680" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="680" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R680" s="12"/>
     </row>
-    <row r="681" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="681" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R681" s="12"/>
     </row>
-    <row r="682" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="682" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R682" s="12"/>
     </row>
-    <row r="683" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="683" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R683" s="12"/>
     </row>
-    <row r="684" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="684" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R684" s="12"/>
     </row>
-    <row r="685" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="685" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R685" s="12"/>
     </row>
-    <row r="686" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="686" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R686" s="12"/>
     </row>
-    <row r="687" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="687" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R687" s="12"/>
     </row>
-    <row r="688" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="688" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R688" s="12"/>
     </row>
-    <row r="689" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="689" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R689" s="12"/>
     </row>
-    <row r="690" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="690" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R690" s="12"/>
     </row>
-    <row r="691" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="691" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R691" s="12"/>
     </row>
-    <row r="692" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="692" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R692" s="12"/>
     </row>
-    <row r="693" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="693" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R693" s="12"/>
     </row>
-    <row r="694" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="694" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R694" s="12"/>
     </row>
-    <row r="695" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="695" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R695" s="12"/>
     </row>
-    <row r="696" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="696" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R696" s="12"/>
     </row>
-    <row r="697" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="697" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R697" s="12"/>
     </row>
-    <row r="698" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="698" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R698" s="12"/>
     </row>
-    <row r="699" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="699" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R699" s="12"/>
     </row>
-    <row r="700" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="700" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R700" s="12"/>
     </row>
-    <row r="701" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="701" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R701" s="12"/>
     </row>
-    <row r="702" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="702" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R702" s="12"/>
     </row>
-    <row r="703" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="703" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R703" s="12"/>
     </row>
-    <row r="704" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="704" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R704" s="12"/>
     </row>
-    <row r="705" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="705" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R705" s="12"/>
     </row>
-    <row r="706" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="706" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R706" s="12"/>
     </row>
-    <row r="707" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="707" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R707" s="12"/>
     </row>
-    <row r="708" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="708" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R708" s="12"/>
     </row>
-    <row r="709" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="709" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R709" s="12"/>
     </row>
-    <row r="710" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="710" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R710" s="12"/>
     </row>
-    <row r="711" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="711" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R711" s="12"/>
     </row>
-    <row r="712" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="712" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R712" s="12"/>
     </row>
-    <row r="713" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="713" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R713" s="12"/>
     </row>
-    <row r="714" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="714" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R714" s="12"/>
     </row>
-    <row r="715" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="715" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R715" s="12"/>
     </row>
-    <row r="716" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="716" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R716" s="12"/>
     </row>
-    <row r="717" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="717" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R717" s="12"/>
     </row>
-    <row r="718" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="718" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R718" s="12"/>
     </row>
-    <row r="719" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="719" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R719" s="12"/>
     </row>
-    <row r="720" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="720" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R720" s="12"/>
     </row>
-    <row r="721" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="721" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R721" s="12"/>
     </row>
-    <row r="722" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="722" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R722" s="12"/>
     </row>
-    <row r="723" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="723" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R723" s="12"/>
     </row>
-    <row r="724" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="724" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R724" s="12"/>
     </row>
-    <row r="725" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="725" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R725" s="12"/>
     </row>
-    <row r="726" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="726" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R726" s="12"/>
     </row>
-    <row r="727" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="727" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R727" s="12"/>
     </row>
-    <row r="728" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="728" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R728" s="12"/>
     </row>
-    <row r="729" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="729" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R729" s="12"/>
     </row>
-    <row r="730" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="730" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R730" s="12"/>
     </row>
-    <row r="731" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="731" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R731" s="12"/>
     </row>
-    <row r="732" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="732" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R732" s="12"/>
     </row>
-    <row r="733" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="733" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R733" s="12"/>
     </row>
-    <row r="734" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="734" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R734" s="12"/>
     </row>
-    <row r="735" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="735" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R735" s="12"/>
     </row>
-    <row r="736" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="736" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R736" s="12"/>
     </row>
-    <row r="737" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="737" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R737" s="12"/>
     </row>
-    <row r="738" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="738" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R738" s="12"/>
     </row>
-    <row r="739" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="739" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R739" s="12"/>
     </row>
-    <row r="740" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="740" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R740" s="12"/>
     </row>
-    <row r="741" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="741" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R741" s="12"/>
     </row>
-    <row r="742" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="742" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R742" s="12"/>
     </row>
-    <row r="743" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="743" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R743" s="12"/>
     </row>
-    <row r="744" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="744" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R744" s="12"/>
     </row>
-    <row r="745" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="745" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R745" s="12"/>
     </row>
-    <row r="746" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="746" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R746" s="12"/>
     </row>
-    <row r="747" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="747" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R747" s="12"/>
     </row>
-    <row r="748" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="748" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R748" s="12"/>
     </row>
-    <row r="749" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="749" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R749" s="12"/>
     </row>
-    <row r="750" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="750" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R750" s="12"/>
     </row>
-    <row r="751" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="751" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R751" s="12"/>
     </row>
-    <row r="752" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="752" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R752" s="12"/>
     </row>
-    <row r="753" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="753" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R753" s="12"/>
     </row>
-    <row r="754" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="754" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R754" s="12"/>
     </row>
-    <row r="755" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="755" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R755" s="12"/>
     </row>
-    <row r="756" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="756" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R756" s="12"/>
     </row>
-    <row r="757" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="757" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R757" s="12"/>
     </row>
-    <row r="758" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="758" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R758" s="12"/>
     </row>
-    <row r="759" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="759" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R759" s="12"/>
     </row>
-    <row r="760" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="760" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R760" s="12"/>
     </row>
-    <row r="761" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="761" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R761" s="12"/>
     </row>
-    <row r="762" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="762" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R762" s="12"/>
     </row>
-    <row r="763" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="763" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R763" s="12"/>
     </row>
-    <row r="764" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="764" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R764" s="12"/>
     </row>
-    <row r="765" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="765" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R765" s="12"/>
     </row>
-    <row r="766" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="766" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R766" s="12"/>
     </row>
-    <row r="767" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="767" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R767" s="12"/>
     </row>
-    <row r="768" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="768" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R768" s="12"/>
     </row>
-    <row r="769" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="769" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R769" s="12"/>
     </row>
-    <row r="770" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="770" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R770" s="12"/>
     </row>
-    <row r="771" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="771" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R771" s="12"/>
     </row>
-    <row r="772" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="772" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R772" s="12"/>
     </row>
-    <row r="773" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="773" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R773" s="12"/>
     </row>
-    <row r="774" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="774" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R774" s="12"/>
     </row>
-    <row r="775" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="775" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R775" s="12"/>
     </row>
-    <row r="776" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="776" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R776" s="12"/>
     </row>
-    <row r="777" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="777" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R777" s="12"/>
     </row>
-    <row r="778" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="778" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R778" s="12"/>
     </row>
-    <row r="779" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="779" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R779" s="12"/>
     </row>
-    <row r="780" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="780" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R780" s="12"/>
     </row>
-    <row r="781" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="781" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R781" s="12"/>
     </row>
-    <row r="782" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="782" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R782" s="12"/>
     </row>
-    <row r="783" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="783" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R783" s="12"/>
     </row>
-    <row r="784" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="784" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R784" s="12"/>
     </row>
-    <row r="785" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="785" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R785" s="12"/>
     </row>
-    <row r="786" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="786" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R786" s="12"/>
     </row>
-    <row r="787" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="787" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R787" s="12"/>
     </row>
-    <row r="788" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="788" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R788" s="12"/>
     </row>
-    <row r="789" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="789" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R789" s="12"/>
     </row>
-    <row r="790" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="790" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R790" s="12"/>
     </row>
-    <row r="791" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="791" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R791" s="12"/>
     </row>
-    <row r="792" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="792" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R792" s="12"/>
     </row>
-    <row r="793" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="793" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R793" s="12"/>
     </row>
-    <row r="794" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="794" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R794" s="12"/>
     </row>
-    <row r="795" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="795" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R795" s="12"/>
     </row>
-    <row r="796" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="796" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R796" s="12"/>
     </row>
-    <row r="797" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="797" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R797" s="12"/>
     </row>
-    <row r="798" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="798" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R798" s="12"/>
     </row>
-    <row r="799" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="799" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R799" s="12"/>
     </row>
-    <row r="800" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="800" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R800" s="12"/>
     </row>
-    <row r="801" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="801" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R801" s="12"/>
     </row>
-    <row r="802" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="802" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R802" s="12"/>
     </row>
-    <row r="803" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="803" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R803" s="12"/>
     </row>
-    <row r="804" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="804" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R804" s="12"/>
     </row>
-    <row r="805" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="805" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R805" s="12"/>
     </row>
-    <row r="806" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="806" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R806" s="12"/>
     </row>
-    <row r="807" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="807" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R807" s="12"/>
     </row>
-    <row r="808" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="808" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R808" s="12"/>
     </row>
-    <row r="809" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="809" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R809" s="12"/>
     </row>
-    <row r="810" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="810" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R810" s="12"/>
     </row>
-    <row r="811" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="811" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R811" s="12"/>
     </row>
-    <row r="812" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="812" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R812" s="12"/>
     </row>
-    <row r="813" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="813" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R813" s="12"/>
     </row>
-    <row r="814" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="814" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R814" s="12"/>
     </row>
-    <row r="815" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="815" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R815" s="12"/>
     </row>
-    <row r="816" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="816" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R816" s="12"/>
     </row>
-    <row r="817" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="817" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R817" s="12"/>
     </row>
-    <row r="818" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="818" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R818" s="12"/>
     </row>
-    <row r="819" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="819" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R819" s="12"/>
     </row>
-    <row r="820" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="820" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R820" s="12"/>
     </row>
-    <row r="821" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="821" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R821" s="12"/>
     </row>
-    <row r="822" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="822" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R822" s="12"/>
     </row>
-    <row r="823" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="823" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R823" s="12"/>
     </row>
-    <row r="824" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="824" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R824" s="12"/>
     </row>
-    <row r="825" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="825" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R825" s="12"/>
     </row>
-    <row r="826" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="826" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R826" s="12"/>
     </row>
-    <row r="827" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="827" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R827" s="12"/>
     </row>
-    <row r="828" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="828" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R828" s="12"/>
     </row>
-    <row r="829" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="829" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R829" s="12"/>
     </row>
-    <row r="830" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="830" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R830" s="12"/>
     </row>
-    <row r="831" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="831" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R831" s="12"/>
     </row>
-    <row r="832" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="832" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R832" s="12"/>
     </row>
-    <row r="833" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="833" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R833" s="12"/>
     </row>
-    <row r="834" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="834" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R834" s="12"/>
     </row>
-    <row r="835" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="835" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R835" s="12"/>
     </row>
-    <row r="836" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="836" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R836" s="12"/>
     </row>
-    <row r="837" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="837" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R837" s="12"/>
     </row>
-    <row r="838" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="838" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R838" s="12"/>
     </row>
-    <row r="839" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="839" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R839" s="12"/>
     </row>
-    <row r="840" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="840" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R840" s="12"/>
     </row>
-    <row r="841" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="841" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R841" s="12"/>
     </row>
-    <row r="842" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="842" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R842" s="12"/>
     </row>
-    <row r="843" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="843" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R843" s="12"/>
     </row>
-    <row r="844" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="844" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R844" s="12"/>
     </row>
-    <row r="845" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="845" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R845" s="12"/>
     </row>
-    <row r="846" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="846" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R846" s="12"/>
     </row>
-    <row r="847" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="847" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R847" s="12"/>
     </row>
-    <row r="848" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="848" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R848" s="12"/>
     </row>
-    <row r="849" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="849" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R849" s="12"/>
     </row>
-    <row r="850" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="850" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R850" s="12"/>
     </row>
-    <row r="851" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="851" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R851" s="12"/>
     </row>
-    <row r="852" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="852" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R852" s="12"/>
     </row>
-    <row r="853" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="853" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R853" s="12"/>
     </row>
-    <row r="854" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="854" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R854" s="12"/>
     </row>
-    <row r="855" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="855" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R855" s="12"/>
     </row>
-    <row r="856" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="856" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R856" s="12"/>
     </row>
-    <row r="857" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="857" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R857" s="12"/>
     </row>
-    <row r="858" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="858" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R858" s="12"/>
     </row>
-    <row r="859" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="859" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R859" s="12"/>
     </row>
-    <row r="860" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="860" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R860" s="12"/>
     </row>
-    <row r="861" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="861" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R861" s="12"/>
     </row>
-    <row r="862" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="862" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R862" s="12"/>
     </row>
-    <row r="863" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="863" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R863" s="12"/>
     </row>
-    <row r="864" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="864" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R864" s="12"/>
     </row>
-    <row r="865" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="865" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R865" s="12"/>
     </row>
-    <row r="866" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="866" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R866" s="12"/>
     </row>
-    <row r="867" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="867" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R867" s="12"/>
     </row>
-    <row r="868" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="868" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R868" s="12"/>
     </row>
-    <row r="869" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="869" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R869" s="12"/>
     </row>
-    <row r="870" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="870" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R870" s="12"/>
     </row>
-    <row r="871" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="871" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R871" s="12"/>
     </row>
-    <row r="872" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="872" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R872" s="12"/>
     </row>
-    <row r="873" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="873" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R873" s="12"/>
     </row>
-    <row r="874" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="874" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R874" s="12"/>
     </row>
-    <row r="875" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="875" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R875" s="12"/>
     </row>
-    <row r="876" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="876" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R876" s="12"/>
     </row>
-    <row r="877" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="877" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R877" s="12"/>
     </row>
-    <row r="878" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="878" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R878" s="12"/>
     </row>
-    <row r="879" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="879" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R879" s="12"/>
     </row>
-    <row r="880" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="880" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R880" s="12"/>
     </row>
-    <row r="881" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="881" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R881" s="12"/>
     </row>
-    <row r="882" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="882" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R882" s="12"/>
     </row>
-    <row r="883" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="883" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R883" s="12"/>
     </row>
-    <row r="884" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="884" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R884" s="12"/>
     </row>
-    <row r="885" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="885" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R885" s="12"/>
     </row>
-    <row r="886" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="886" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R886" s="12"/>
     </row>
-    <row r="887" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="887" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R887" s="12"/>
     </row>
-    <row r="888" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="888" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R888" s="12"/>
     </row>
-    <row r="889" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="889" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R889" s="12"/>
     </row>
-    <row r="890" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="890" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R890" s="12"/>
     </row>
-    <row r="891" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="891" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R891" s="12"/>
     </row>
-    <row r="892" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="892" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R892" s="12"/>
     </row>
-    <row r="893" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="893" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R893" s="12"/>
     </row>
-    <row r="894" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="894" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R894" s="12"/>
     </row>
-    <row r="895" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="895" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R895" s="12"/>
     </row>
-    <row r="896" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="896" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R896" s="12"/>
     </row>
-    <row r="897" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="897" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R897" s="12"/>
     </row>
-    <row r="898" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="898" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R898" s="12"/>
     </row>
-    <row r="899" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="899" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R899" s="12"/>
     </row>
-    <row r="900" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="900" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R900" s="12"/>
     </row>
-    <row r="901" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="901" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R901" s="12"/>
     </row>
-    <row r="902" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="902" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R902" s="12"/>
     </row>
-    <row r="903" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="903" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R903" s="12"/>
     </row>
-    <row r="904" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="904" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R904" s="12"/>
     </row>
-    <row r="905" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="905" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R905" s="12"/>
     </row>
-    <row r="906" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="906" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R906" s="12"/>
     </row>
-    <row r="907" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="907" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R907" s="12"/>
     </row>
-    <row r="908" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="908" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R908" s="12"/>
     </row>
-    <row r="909" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="909" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R909" s="12"/>
     </row>
-    <row r="910" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="910" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R910" s="12"/>
     </row>
-    <row r="911" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="911" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R911" s="12"/>
     </row>
-    <row r="912" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="912" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R912" s="12"/>
     </row>
-    <row r="913" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="913" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R913" s="12"/>
     </row>
-    <row r="914" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="914" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R914" s="12"/>
     </row>
-    <row r="915" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="915" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R915" s="12"/>
     </row>
-    <row r="916" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="916" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R916" s="12"/>
     </row>
-    <row r="917" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="917" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R917" s="12"/>
     </row>
-    <row r="918" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="918" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R918" s="12"/>
     </row>
-    <row r="919" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="919" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R919" s="12"/>
     </row>
-    <row r="920" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="920" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R920" s="12"/>
     </row>
-    <row r="921" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="921" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R921" s="12"/>
     </row>
-    <row r="922" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="922" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R922" s="12"/>
     </row>
-    <row r="923" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="923" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R923" s="12"/>
     </row>
-    <row r="924" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="924" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R924" s="12"/>
     </row>
-    <row r="925" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="925" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R925" s="12"/>
     </row>
-    <row r="926" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="926" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R926" s="12"/>
     </row>
-    <row r="927" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="927" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R927" s="12"/>
     </row>
-    <row r="928" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="928" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R928" s="12"/>
     </row>
-    <row r="929" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="929" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R929" s="12"/>
     </row>
-    <row r="930" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="930" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R930" s="12"/>
     </row>
-    <row r="931" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="931" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R931" s="12"/>
     </row>
-    <row r="932" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="932" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R932" s="12"/>
     </row>
-    <row r="933" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="933" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R933" s="12"/>
     </row>
-    <row r="934" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="934" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R934" s="12"/>
     </row>
-    <row r="935" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="935" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R935" s="12"/>
     </row>
-    <row r="936" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="936" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R936" s="12"/>
     </row>
-    <row r="937" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="937" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R937" s="12"/>
     </row>
-    <row r="938" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="938" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R938" s="12"/>
     </row>
-    <row r="939" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="939" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R939" s="12"/>
     </row>
-    <row r="940" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="940" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R940" s="12"/>
     </row>
-    <row r="941" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="941" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R941" s="12"/>
     </row>
-    <row r="942" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="942" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R942" s="12"/>
     </row>
-    <row r="943" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="943" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R943" s="12"/>
     </row>
-    <row r="944" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="944" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R944" s="12"/>
     </row>
-    <row r="945" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="945" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R945" s="12"/>
     </row>
-    <row r="946" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="946" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R946" s="12"/>
     </row>
-    <row r="947" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="947" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R947" s="12"/>
     </row>
-    <row r="948" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="948" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R948" s="12"/>
     </row>
-    <row r="949" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="949" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R949" s="12"/>
     </row>
-    <row r="950" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="950" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R950" s="12"/>
     </row>
-    <row r="951" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="951" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R951" s="12"/>
     </row>
-    <row r="952" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="952" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R952" s="12"/>
     </row>
-    <row r="953" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="953" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R953" s="12"/>
     </row>
-    <row r="954" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="954" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R954" s="12"/>
     </row>
-    <row r="955" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="955" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R955" s="12"/>
     </row>
-    <row r="956" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="956" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R956" s="12"/>
     </row>
-    <row r="957" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="957" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R957" s="12"/>
     </row>
-    <row r="958" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="958" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R958" s="12"/>
     </row>
-    <row r="959" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="959" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R959" s="12"/>
     </row>
-    <row r="960" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="960" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R960" s="12"/>
     </row>
-    <row r="961" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="961" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R961" s="12"/>
     </row>
-    <row r="962" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="962" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R962" s="12"/>
     </row>
-    <row r="963" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="963" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R963" s="12"/>
     </row>
-    <row r="964" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="964" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R964" s="12"/>
     </row>
-    <row r="965" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="965" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R965" s="12"/>
     </row>
-    <row r="966" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="966" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R966" s="12"/>
     </row>
-    <row r="967" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="967" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R967" s="12"/>
     </row>
-    <row r="968" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="968" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R968" s="12"/>
     </row>
-    <row r="969" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="969" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R969" s="12"/>
     </row>
-    <row r="970" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="970" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R970" s="12"/>
     </row>
-    <row r="971" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="971" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R971" s="12"/>
     </row>
-    <row r="972" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="972" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R972" s="12"/>
     </row>
-    <row r="973" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="973" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R973" s="12"/>
     </row>
-    <row r="974" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="974" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R974" s="12"/>
     </row>
-    <row r="975" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="975" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R975" s="12"/>
     </row>
-    <row r="976" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="976" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R976" s="12"/>
     </row>
-    <row r="977" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="977" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R977" s="12"/>
     </row>
-    <row r="978" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="978" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R978" s="12"/>
     </row>
-    <row r="979" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="979" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R979" s="12"/>
     </row>
-    <row r="980" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="980" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R980" s="12"/>
     </row>
-    <row r="981" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="981" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R981" s="12"/>
     </row>
-    <row r="982" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="982" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R982" s="12"/>
     </row>
-    <row r="983" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="983" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R983" s="12"/>
     </row>
-    <row r="984" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="984" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R984" s="12"/>
     </row>
-    <row r="985" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="985" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R985" s="12"/>
     </row>
-    <row r="986" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="986" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R986" s="12"/>
     </row>
-    <row r="987" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="987" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R987" s="12"/>
     </row>
-    <row r="988" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="988" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R988" s="12"/>
     </row>
-    <row r="989" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="989" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R989" s="12"/>
     </row>
-    <row r="990" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="990" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R990" s="12"/>
     </row>
-    <row r="991" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="991" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R991" s="12"/>
     </row>
-    <row r="992" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="992" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R992" s="12"/>
     </row>
-    <row r="993" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="993" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R993" s="12"/>
     </row>
-    <row r="994" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="994" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R994" s="12"/>
     </row>
-    <row r="995" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="995" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R995" s="12"/>
     </row>
-    <row r="996" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="996" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R996" s="12"/>
     </row>
-    <row r="997" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="997" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R997" s="12"/>
     </row>
-    <row r="998" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="998" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R998" s="12"/>
     </row>
-    <row r="999" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="999" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R999" s="12"/>
     </row>
-    <row r="1000" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1000" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1000" s="12"/>
     </row>
-    <row r="1001" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1001" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1001" s="12"/>
     </row>
-    <row r="1002" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1002" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1002" s="12"/>
     </row>
-    <row r="1003" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1003" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1003" s="12"/>
     </row>
-    <row r="1004" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1004" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1004" s="12"/>
     </row>
-    <row r="1005" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1005" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1005" s="12"/>
     </row>
-    <row r="1006" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1006" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1006" s="12"/>
     </row>
-    <row r="1007" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1007" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1007" s="12"/>
     </row>
-    <row r="1008" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1008" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1008" s="12"/>
     </row>
-    <row r="1009" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1009" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1009" s="12"/>
     </row>
-    <row r="1010" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1010" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1010" s="12"/>
     </row>
-    <row r="1011" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1011" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1011" s="12"/>
     </row>
-    <row r="1012" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1012" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1012" s="12"/>
     </row>
-    <row r="1013" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1013" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1013" s="12"/>
     </row>
-    <row r="1014" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1014" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1014" s="12"/>
     </row>
-    <row r="1015" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1015" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1015" s="12"/>
     </row>
-    <row r="1016" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1016" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1016" s="12"/>
     </row>
-    <row r="1017" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1017" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1017" s="12"/>
     </row>
-    <row r="1018" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1018" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1018" s="12"/>
     </row>
-    <row r="1019" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1019" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1019" s="12"/>
     </row>
-    <row r="1020" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1020" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1020" s="12"/>
     </row>
-    <row r="1021" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1021" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1021" s="12"/>
     </row>
-    <row r="1022" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1022" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1022" s="12"/>
     </row>
-    <row r="1023" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1023" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1023" s="12"/>
     </row>
-    <row r="1024" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1024" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1024" s="12"/>
     </row>
-    <row r="1025" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1025" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1025" s="12"/>
     </row>
-    <row r="1026" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1026" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1026" s="12"/>
     </row>
-    <row r="1027" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1027" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1027" s="12"/>
     </row>
-    <row r="1028" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1028" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1028" s="12"/>
     </row>
-    <row r="1029" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1029" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1029" s="12"/>
     </row>
-    <row r="1030" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1030" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1030" s="12"/>
     </row>
-    <row r="1031" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1031" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1031" s="12"/>
     </row>
-    <row r="1032" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1032" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1032" s="12"/>
     </row>
-    <row r="1033" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1033" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1033" s="12"/>
     </row>
-    <row r="1034" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1034" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1034" s="12"/>
     </row>
-    <row r="1035" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1035" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1035" s="12"/>
     </row>
-    <row r="1036" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1036" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1036" s="12"/>
     </row>
-    <row r="1037" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1037" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1037" s="12"/>
     </row>
-    <row r="1038" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1038" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1038" s="12"/>
     </row>
-    <row r="1039" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1039" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1039" s="12"/>
     </row>
-    <row r="1040" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1040" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1040" s="12"/>
     </row>
-    <row r="1041" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1041" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1041" s="12"/>
     </row>
-    <row r="1042" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1042" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1042" s="12"/>
     </row>
-    <row r="1043" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1043" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1043" s="12"/>
     </row>
-    <row r="1044" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1044" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1044" s="12"/>
     </row>
-    <row r="1045" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1045" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1045" s="12"/>
     </row>
-    <row r="1046" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1046" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1046" s="12"/>
     </row>
-    <row r="1047" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1047" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1047" s="12"/>
     </row>
-    <row r="1048" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1048" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1048" s="12"/>
     </row>
-    <row r="1049" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1049" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1049" s="12"/>
     </row>
-    <row r="1050" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1050" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1050" s="12"/>
     </row>
-    <row r="1051" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1051" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1051" s="12"/>
     </row>
-    <row r="1052" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1052" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1052" s="12"/>
     </row>
-    <row r="1053" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1053" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1053" s="12"/>
     </row>
-    <row r="1054" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1054" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1054" s="12"/>
     </row>
-    <row r="1055" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1055" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1055" s="12"/>
     </row>
-    <row r="1056" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1056" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1056" s="12"/>
     </row>
-    <row r="1057" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1057" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1057" s="12"/>
     </row>
-    <row r="1058" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1058" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1058" s="12"/>
     </row>
-    <row r="1059" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1059" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1059" s="12"/>
     </row>
-    <row r="1060" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1060" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1060" s="12"/>
     </row>
-    <row r="1061" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1061" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1061" s="12"/>
     </row>
-    <row r="1062" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1062" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1062" s="12"/>
     </row>
-    <row r="1063" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1063" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1063" s="12"/>
     </row>
-    <row r="1064" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1064" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1064" s="12"/>
     </row>
-    <row r="1065" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1065" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1065" s="12"/>
     </row>
-    <row r="1066" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1066" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1066" s="12"/>
     </row>
-    <row r="1067" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1067" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1067" s="12"/>
     </row>
-    <row r="1068" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1068" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1068" s="12"/>
     </row>
-    <row r="1069" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1069" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1069" s="12"/>
     </row>
-    <row r="1070" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1070" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1070" s="12"/>
     </row>
-    <row r="1071" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1071" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1071" s="12"/>
     </row>
-    <row r="1072" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1072" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1072" s="12"/>
     </row>
-    <row r="1073" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1073" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1073" s="12"/>
     </row>
-    <row r="1074" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1074" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1074" s="12"/>
     </row>
-    <row r="1075" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1075" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1075" s="12"/>
     </row>
-    <row r="1076" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1076" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1076" s="12"/>
     </row>
-    <row r="1077" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1077" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1077" s="12"/>
     </row>
-    <row r="1078" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1078" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1078" s="12"/>
     </row>
-    <row r="1079" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1079" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1079" s="12"/>
     </row>
-    <row r="1080" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1080" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1080" s="12"/>
     </row>
-    <row r="1081" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1081" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1081" s="12"/>
     </row>
-    <row r="1082" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1082" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1082" s="12"/>
     </row>
-    <row r="1083" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1083" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1083" s="12"/>
     </row>
-    <row r="1084" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1084" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1084" s="12"/>
     </row>
-    <row r="1085" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1085" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1085" s="12"/>
     </row>
-    <row r="1086" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1086" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1086" s="12"/>
     </row>
-    <row r="1087" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1087" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1087" s="12"/>
     </row>
-    <row r="1088" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1088" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1088" s="12"/>
     </row>
-    <row r="1089" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1089" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1089" s="12"/>
     </row>
-    <row r="1090" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1090" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1090" s="12"/>
     </row>
-    <row r="1091" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1091" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1091" s="12"/>
     </row>
-    <row r="1092" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1092" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1092" s="12"/>
     </row>
-    <row r="1093" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1093" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1093" s="12"/>
     </row>
-    <row r="1094" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1094" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1094" s="12"/>
     </row>
-    <row r="1095" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1095" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1095" s="12"/>
     </row>
-    <row r="1096" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1096" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1096" s="12"/>
     </row>
-    <row r="1097" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1097" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1097" s="12"/>
     </row>
-    <row r="1098" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1098" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1098" s="12"/>
     </row>
-    <row r="1099" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1099" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1099" s="12"/>
     </row>
-    <row r="1100" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1100" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1100" s="12"/>
     </row>
-    <row r="1101" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1101" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1101" s="12"/>
     </row>
-    <row r="1102" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1102" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1102" s="12"/>
     </row>
-    <row r="1103" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1103" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1103" s="12"/>
     </row>
-    <row r="1104" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1104" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1104" s="12"/>
     </row>
-    <row r="1105" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1105" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1105" s="12"/>
     </row>
-    <row r="1106" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1106" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1106" s="12"/>
     </row>
-    <row r="1107" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1107" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1107" s="12"/>
     </row>
-    <row r="1108" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1108" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1108" s="12"/>
     </row>
-    <row r="1109" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1109" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1109" s="12"/>
     </row>
-    <row r="1110" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1110" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1110" s="12"/>
     </row>
-    <row r="1111" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1111" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1111" s="12"/>
     </row>
-    <row r="1112" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1112" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1112" s="12"/>
     </row>
-    <row r="1113" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1113" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1113" s="12"/>
     </row>
-    <row r="1114" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1114" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1114" s="12"/>
     </row>
-    <row r="1115" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1115" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1115" s="12"/>
     </row>
-    <row r="1116" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1116" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1116" s="12"/>
     </row>
-    <row r="1117" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1117" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1117" s="12"/>
     </row>
-    <row r="1118" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1118" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1118" s="12"/>
     </row>
-    <row r="1119" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1119" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1119" s="12"/>
     </row>
-    <row r="1120" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1120" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1120" s="12"/>
     </row>
-    <row r="1121" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1121" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1121" s="12"/>
     </row>
-    <row r="1122" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1122" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1122" s="12"/>
     </row>
-    <row r="1123" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1123" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1123" s="12"/>
     </row>
-    <row r="1124" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1124" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1124" s="12"/>
     </row>
-    <row r="1125" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1125" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1125" s="12"/>
     </row>
-    <row r="1126" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1126" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1126" s="12"/>
     </row>
-    <row r="1127" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1127" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1127" s="12"/>
     </row>
-    <row r="1128" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1128" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1128" s="12"/>
     </row>
-    <row r="1129" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1129" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1129" s="12"/>
     </row>
-    <row r="1130" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1130" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1130" s="12"/>
     </row>
-    <row r="1131" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1131" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1131" s="12"/>
     </row>
-    <row r="1132" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1132" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1132" s="12"/>
     </row>
-    <row r="1133" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1133" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1133" s="12"/>
     </row>
-    <row r="1134" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1134" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1134" s="12"/>
     </row>
-    <row r="1135" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1135" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1135" s="12"/>
     </row>
-    <row r="1136" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1136" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1136" s="12"/>
     </row>
-    <row r="1137" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1137" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1137" s="12"/>
     </row>
-    <row r="1138" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1138" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1138" s="12"/>
     </row>
-    <row r="1139" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1139" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1139" s="12"/>
     </row>
-    <row r="1140" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1140" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1140" s="12"/>
     </row>
-    <row r="1141" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1141" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1141" s="12"/>
     </row>
-    <row r="1142" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1142" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1142" s="12"/>
     </row>
-    <row r="1143" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1143" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1143" s="12"/>
     </row>
-    <row r="1144" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1144" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1144" s="12"/>
     </row>
-    <row r="1145" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1145" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1145" s="12"/>
     </row>
-    <row r="1146" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1146" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1146" s="12"/>
     </row>
-    <row r="1147" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1147" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1147" s="12"/>
     </row>
-    <row r="1148" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1148" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1148" s="12"/>
     </row>
-    <row r="1149" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1149" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1149" s="12"/>
     </row>
-    <row r="1150" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1150" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1150" s="12"/>
     </row>
-    <row r="1151" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1151" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1151" s="12"/>
     </row>
-    <row r="1152" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1152" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1152" s="12"/>
     </row>
-    <row r="1153" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1153" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1153" s="12"/>
     </row>
-    <row r="1154" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1154" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1154" s="12"/>
     </row>
-    <row r="1155" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1155" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1155" s="12"/>
     </row>
-    <row r="1156" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1156" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1156" s="12"/>
     </row>
-    <row r="1157" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1157" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1157" s="12"/>
     </row>
-    <row r="1158" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1158" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1158" s="12"/>
     </row>
-    <row r="1159" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1159" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1159" s="12"/>
     </row>
-    <row r="1160" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1160" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1160" s="12"/>
     </row>
-    <row r="1161" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1161" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1161" s="12"/>
     </row>
-    <row r="1162" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1162" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1162" s="12"/>
     </row>
-    <row r="1163" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1163" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1163" s="12"/>
     </row>
-    <row r="1164" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1164" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1164" s="12"/>
     </row>
-    <row r="1165" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1165" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1165" s="12"/>
     </row>
-    <row r="1166" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1166" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1166" s="12"/>
     </row>
-    <row r="1167" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1167" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1167" s="12"/>
     </row>
-    <row r="1168" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1168" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1168" s="12"/>
     </row>
-    <row r="1169" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1169" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1169" s="12"/>
     </row>
-    <row r="1170" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1170" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1170" s="12"/>
     </row>
-    <row r="1171" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1171" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1171" s="12"/>
     </row>
-    <row r="1172" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1172" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1172" s="12"/>
     </row>
-    <row r="1173" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1173" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1173" s="12"/>
     </row>
-    <row r="1174" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1174" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1174" s="12"/>
     </row>
-    <row r="1175" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1175" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1175" s="12"/>
     </row>
-    <row r="1176" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1176" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1176" s="12"/>
     </row>
-    <row r="1177" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1177" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1177" s="12"/>
     </row>
-    <row r="1178" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1178" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1178" s="12"/>
     </row>
-    <row r="1179" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1179" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1179" s="12"/>
     </row>
-    <row r="1180" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1180" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1180" s="12"/>
     </row>
-    <row r="1181" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1181" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1181" s="12"/>
     </row>
-    <row r="1182" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1182" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1182" s="12"/>
     </row>
-    <row r="1183" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1183" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1183" s="12"/>
     </row>
-    <row r="1184" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1184" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1184" s="12"/>
     </row>
-    <row r="1185" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1185" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1185" s="12"/>
     </row>
-    <row r="1186" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1186" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1186" s="12"/>
     </row>
-    <row r="1187" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1187" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1187" s="12"/>
     </row>
-    <row r="1188" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1188" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1188" s="12"/>
     </row>
-    <row r="1189" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1189" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1189" s="12"/>
     </row>
-    <row r="1190" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1190" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1190" s="12"/>
     </row>
-    <row r="1191" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1191" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1191" s="12"/>
     </row>
-    <row r="1192" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1192" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1192" s="12"/>
     </row>
-    <row r="1193" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1193" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1193" s="12"/>
     </row>
-    <row r="1194" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1194" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1194" s="12"/>
     </row>
-    <row r="1195" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1195" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1195" s="12"/>
     </row>
-    <row r="1196" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1196" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1196" s="12"/>
     </row>
-    <row r="1197" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1197" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1197" s="12"/>
     </row>
-    <row r="1198" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1198" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1198" s="12"/>
     </row>
-    <row r="1199" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1199" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1199" s="12"/>
     </row>
-    <row r="1200" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1200" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1200" s="12"/>
     </row>
-    <row r="1201" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1201" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1201" s="12"/>
     </row>
-    <row r="1202" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1202" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1202" s="12"/>
     </row>
-    <row r="1203" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1203" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1203" s="12"/>
     </row>
-    <row r="1204" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1204" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1204" s="12"/>
     </row>
-    <row r="1205" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1205" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1205" s="12"/>
     </row>
-    <row r="1206" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1206" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1206" s="12"/>
     </row>
-    <row r="1207" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1207" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1207" s="12"/>
     </row>
-    <row r="1208" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1208" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1208" s="12"/>
     </row>
-    <row r="1209" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1209" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1209" s="12"/>
     </row>
-    <row r="1210" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1210" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1210" s="12"/>
     </row>
-    <row r="1211" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1211" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1211" s="12"/>
     </row>
-    <row r="1212" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1212" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1212" s="12"/>
     </row>
-    <row r="1213" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1213" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1213" s="12"/>
     </row>
-    <row r="1214" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1214" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1214" s="12"/>
     </row>
-    <row r="1215" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1215" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1215" s="12"/>
     </row>
-    <row r="1216" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1216" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1216" s="12"/>
     </row>
-    <row r="1217" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1217" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1217" s="12"/>
     </row>
-    <row r="1218" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1218" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1218" s="12"/>
     </row>
-    <row r="1219" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1219" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1219" s="12"/>
     </row>
-    <row r="1220" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1220" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1220" s="12"/>
     </row>
-    <row r="1221" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1221" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1221" s="12"/>
     </row>
-    <row r="1222" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1222" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1222" s="12"/>
     </row>
-    <row r="1223" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1223" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1223" s="12"/>
     </row>
-    <row r="1224" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1224" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1224" s="12"/>
     </row>
-    <row r="1225" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1225" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1225" s="12"/>
     </row>
-    <row r="1226" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1226" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1226" s="12"/>
     </row>
-    <row r="1227" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1227" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1227" s="12"/>
     </row>
-    <row r="1228" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1228" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1228" s="12"/>
     </row>
-    <row r="1229" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1229" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1229" s="12"/>
     </row>
-    <row r="1230" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1230" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1230" s="12"/>
     </row>
-    <row r="1231" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1231" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1231" s="12"/>
     </row>
-    <row r="1232" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1232" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1232" s="12"/>
     </row>
-    <row r="1233" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1233" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1233" s="12"/>
     </row>
-    <row r="1234" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1234" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1234" s="12"/>
     </row>
-    <row r="1235" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1235" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1235" s="12"/>
     </row>
-    <row r="1236" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1236" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1236" s="12"/>
     </row>
-    <row r="1237" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1237" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1237" s="12"/>
     </row>
-    <row r="1238" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1238" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1238" s="12"/>
     </row>
-    <row r="1239" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1239" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1239" s="12"/>
     </row>
-    <row r="1240" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1240" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1240" s="12"/>
     </row>
-    <row r="1241" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1241" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1241" s="12"/>
     </row>
-    <row r="1242" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1242" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1242" s="12"/>
     </row>
-    <row r="1243" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1243" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1243" s="12"/>
     </row>
-    <row r="1244" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1244" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1244" s="12"/>
     </row>
-    <row r="1245" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1245" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1245" s="12"/>
     </row>
-    <row r="1246" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1246" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1246" s="12"/>
     </row>
-    <row r="1247" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1247" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1247" s="12"/>
     </row>
-    <row r="1248" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1248" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1248" s="12"/>
     </row>
-    <row r="1249" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1249" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1249" s="12"/>
     </row>
-    <row r="1250" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1250" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1250" s="12"/>
     </row>
-    <row r="1251" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1251" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1251" s="12"/>
     </row>
-    <row r="1252" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1252" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1252" s="12"/>
     </row>
-    <row r="1253" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1253" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1253" s="12"/>
     </row>
-    <row r="1254" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1254" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1254" s="12"/>
     </row>
-    <row r="1255" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1255" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1255" s="12"/>
     </row>
-    <row r="1256" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1256" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1256" s="12"/>
     </row>
-    <row r="1257" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1257" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1257" s="12"/>
     </row>
-    <row r="1258" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1258" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1258" s="12"/>
     </row>
-    <row r="1259" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1259" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1259" s="12"/>
     </row>
-    <row r="1260" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1260" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1260" s="12"/>
     </row>
-    <row r="1261" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1261" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1261" s="12"/>
     </row>
-    <row r="1262" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1262" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1262" s="12"/>
     </row>
-    <row r="1263" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1263" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1263" s="12"/>
     </row>
-    <row r="1264" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1264" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1264" s="12"/>
     </row>
-    <row r="1265" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1265" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1265" s="12"/>
     </row>
-    <row r="1266" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1266" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1266" s="12"/>
     </row>
-    <row r="1267" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1267" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1267" s="12"/>
     </row>
-    <row r="1268" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1268" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1268" s="12"/>
     </row>
-    <row r="1269" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1269" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1269" s="12"/>
     </row>
-    <row r="1270" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1270" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1270" s="12"/>
     </row>
-    <row r="1271" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1271" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1271" s="12"/>
     </row>
-    <row r="1272" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1272" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1272" s="12"/>
     </row>
-    <row r="1273" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1273" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1273" s="12"/>
     </row>
-    <row r="1274" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1274" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1274" s="12"/>
     </row>
-    <row r="1275" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1275" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1275" s="12"/>
     </row>
-    <row r="1276" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1276" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1276" s="12"/>
     </row>
-    <row r="1277" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1277" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1277" s="12"/>
     </row>
-    <row r="1278" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1278" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1278" s="12"/>
     </row>
-    <row r="1279" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1279" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1279" s="12"/>
     </row>
-    <row r="1280" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1280" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1280" s="12"/>
     </row>
-    <row r="1281" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1281" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1281" s="12"/>
     </row>
-    <row r="1282" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1282" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1282" s="12"/>
     </row>
-    <row r="1283" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1283" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1283" s="12"/>
     </row>
-    <row r="1284" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1284" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1284" s="12"/>
     </row>
-    <row r="1285" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1285" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1285" s="12"/>
     </row>
-    <row r="1286" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1286" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1286" s="12"/>
     </row>
-    <row r="1287" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1287" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1287" s="12"/>
     </row>
-    <row r="1288" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1288" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1288" s="12"/>
     </row>
-    <row r="1289" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1289" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1289" s="12"/>
     </row>
-    <row r="1290" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1290" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1290" s="12"/>
     </row>
-    <row r="1291" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1291" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1291" s="12"/>
     </row>
-    <row r="1292" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1292" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1292" s="12"/>
     </row>
-    <row r="1293" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1293" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1293" s="12"/>
     </row>
-    <row r="1294" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1294" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1294" s="12"/>
     </row>
-    <row r="1295" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1295" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1295" s="12"/>
     </row>
-    <row r="1296" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1296" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1296" s="12"/>
     </row>
-    <row r="1297" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1297" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1297" s="12"/>
     </row>
-    <row r="1298" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1298" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1298" s="12"/>
     </row>
-    <row r="1299" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1299" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1299" s="12"/>
     </row>
-    <row r="1300" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1300" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1300" s="12"/>
     </row>
-    <row r="1301" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1301" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1301" s="12"/>
     </row>
-    <row r="1302" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1302" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1302" s="12"/>
     </row>
-    <row r="1303" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1303" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1303" s="12"/>
     </row>
-    <row r="1304" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1304" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1304" s="12"/>
     </row>
-    <row r="1305" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1305" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1305" s="12"/>
     </row>
-    <row r="1306" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1306" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1306" s="12"/>
     </row>
-    <row r="1307" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1307" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1307" s="12"/>
     </row>
-    <row r="1308" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1308" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1308" s="12"/>
     </row>
-    <row r="1309" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1309" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1309" s="12"/>
     </row>
-    <row r="1310" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1310" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1310" s="12"/>
     </row>
-    <row r="1311" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1311" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1311" s="12"/>
     </row>
-    <row r="1312" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1312" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1312" s="12"/>
     </row>
-    <row r="1313" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1313" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1313" s="12"/>
     </row>
-    <row r="1314" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1314" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1314" s="12"/>
     </row>
-    <row r="1315" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1315" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1315" s="12"/>
     </row>
-    <row r="1316" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1316" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1316" s="12"/>
     </row>
-    <row r="1317" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1317" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1317" s="12"/>
     </row>
-    <row r="1318" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1318" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1318" s="12"/>
     </row>
-    <row r="1319" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1319" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1319" s="12"/>
     </row>
-    <row r="1320" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1320" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1320" s="12"/>
     </row>
-    <row r="1321" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1321" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1321" s="12"/>
     </row>
-    <row r="1322" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1322" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1322" s="12"/>
     </row>
-    <row r="1323" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1323" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1323" s="12"/>
     </row>
-    <row r="1324" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1324" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1324" s="12"/>
     </row>
-    <row r="1325" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1325" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1325" s="12"/>
     </row>
-    <row r="1326" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1326" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1326" s="12"/>
     </row>
-    <row r="1327" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1327" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1327" s="12"/>
     </row>
-    <row r="1328" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1328" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1328" s="12"/>
     </row>
-    <row r="1329" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1329" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1329" s="12"/>
     </row>
-    <row r="1330" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1330" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1330" s="12"/>
     </row>
-    <row r="1331" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1331" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1331" s="12"/>
     </row>
-    <row r="1332" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1332" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1332" s="12"/>
     </row>
-    <row r="1333" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1333" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1333" s="12"/>
     </row>
-    <row r="1334" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1334" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1334" s="12"/>
     </row>
-    <row r="1335" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1335" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1335" s="12"/>
     </row>
-    <row r="1336" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1336" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1336" s="12"/>
     </row>
-    <row r="1337" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1337" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1337" s="12"/>
     </row>
-    <row r="1338" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1338" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1338" s="12"/>
     </row>
-    <row r="1339" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1339" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1339" s="12"/>
     </row>
-    <row r="1340" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1340" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1340" s="12"/>
     </row>
-    <row r="1341" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1341" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1341" s="12"/>
     </row>
-    <row r="1342" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="1342" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R1342" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2026:R1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2026:R1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>города</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Тип_доставки</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>список_температур</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>документы</formula1>
     </dataValidation>
   </dataValidations>
@@ -4861,7 +4862,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>'Списки (не трогать)'!$A$2:$A$7</xm:f>
           </x14:formula1>
@@ -4874,17 +4875,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="2" width="26.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.09765625" customWidth="1"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -4898,7 +4899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -4912,7 +4913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -4937,17 +4938,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -4959,40 +4960,40 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B3:N26"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.8984375" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.09765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.25" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>37</v>
       </c>
@@ -5007,13 +5008,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="K7" s="5"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>41</v>
       </c>
@@ -5021,7 +5022,7 @@
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>42</v>
       </c>
@@ -5029,12 +5030,12 @@
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>43</v>
       </c>
@@ -5042,17 +5043,17 @@
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -5068,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>48</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>50</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>52</v>
       </c>
@@ -5092,7 +5093,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>53</v>
       </c>
@@ -5100,29 +5101,29 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>54</v>
       </c>
       <c r="D21" s="7">
         <f ca="1">TODAY()</f>
-        <v>45964</v>
+        <v>46097</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>61</v>
       </c>

--- a/blankimport.xlsx
+++ b/blankimport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grillman\go\warehouseHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ED1A00-6F15-4462-8A48-E21EF21DB2A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C652DA17-6ABF-4B66-8A43-FBCE2D914F12}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D21" s="7">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="F21" t="s">
         <v>54</v>
